--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>sale_price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -462,6 +467,11 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -479,6 +489,11 @@
           <t>£375.00</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,6 +511,11 @@
           <t>£113.28</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,6 +533,11 @@
           <t>£188.94</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -530,6 +555,11 @@
           <t>£382.07</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -547,6 +577,11 @@
           <t>£442.36</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -564,6 +599,11 @@
           <t>£711.85</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -581,6 +621,11 @@
           <t>£201.57</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -598,6 +643,11 @@
           <t>£410.82</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -615,6 +665,11 @@
           <t>£727.23</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -632,6 +687,11 @@
           <t>£282.29</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -649,6 +709,11 @@
           <t>£357.92</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -666,6 +731,11 @@
           <t>£410.93</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -683,6 +753,11 @@
           <t>£391.49</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -700,6 +775,11 @@
           <t>£447.74</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -717,6 +797,11 @@
           <t>£526.53</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -734,6 +819,11 @@
           <t>£630.21</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -751,6 +841,11 @@
           <t>£798.41</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -768,6 +863,11 @@
           <t>£398.06</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -785,6 +885,11 @@
           <t>£438.42</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -802,6 +907,11 @@
           <t>£444.71</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -819,6 +929,11 @@
           <t>£480.15</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -836,6 +951,11 @@
           <t>£500.21</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -853,6 +973,11 @@
           <t>£540.50</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -870,6 +995,11 @@
           <t>£701.67</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -887,6 +1017,11 @@
           <t>£406.45</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -904,6 +1039,11 @@
           <t>£501.19</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -921,6 +1061,11 @@
           <t>£538.19</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -938,6 +1083,11 @@
           <t>£672.95</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -955,6 +1105,11 @@
           <t>£872.04</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -972,6 +1127,11 @@
           <t>£1,097.36</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -989,6 +1149,11 @@
           <t>£483.65</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1006,6 +1171,11 @@
           <t>£756.12</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1023,6 +1193,11 @@
           <t>£1,219.98</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1040,6 +1215,11 @@
           <t>£1,366.54</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1055,6 +1235,11 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>£818.47</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,6 +1273,11 @@
           <t>sale_price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1101,6 +1291,11 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1118,6 +1313,11 @@
           <t>£102.07</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1135,6 +1335,11 @@
           <t>£172.36</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1152,6 +1357,11 @@
           <t>£347.24</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1169,6 +1379,11 @@
           <t>£403.58</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1186,6 +1401,11 @@
           <t>£646.58</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1203,6 +1423,11 @@
           <t>£183.35</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1220,6 +1445,11 @@
           <t>£371.27</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1237,6 +1467,11 @@
           <t>£661.78</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,6 +1489,11 @@
           <t>£257.36</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1271,6 +1511,11 @@
           <t>£327.14</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1288,6 +1533,11 @@
           <t>£372.78</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1305,6 +1555,11 @@
           <t>£357.65</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1322,6 +1577,11 @@
           <t>£407.32</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1339,6 +1599,11 @@
           <t>£477.51</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1356,6 +1621,11 @@
           <t>£571.00</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1373,6 +1643,11 @@
           <t>£725.04</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1390,6 +1665,11 @@
           <t>£362.37</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1407,6 +1687,11 @@
           <t>£398.05</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1424,6 +1709,11 @@
           <t>£403.39</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1441,6 +1731,11 @@
           <t>£435.76</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1458,6 +1753,11 @@
           <t>£454.31</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1475,6 +1775,11 @@
           <t>£490.40</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1492,6 +1797,11 @@
           <t>£637.25</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1509,6 +1819,11 @@
           <t>£369.34</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1526,6 +1841,11 @@
           <t>£456.80</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1543,6 +1863,11 @@
           <t>£491.12</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1560,6 +1885,11 @@
           <t>£612.24</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1577,6 +1907,11 @@
           <t>£792.43</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1594,6 +1929,11 @@
           <t>£1,104.29</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1611,6 +1951,11 @@
           <t>£438.42</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1628,6 +1973,11 @@
           <t>£686.56</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1645,6 +1995,11 @@
           <t>£1,108.85</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1662,6 +2017,11 @@
           <t>£1,369.18</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1679,6 +2039,11 @@
           <t>£821.76</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1696,6 +2061,11 @@
           <t>£1,164.84</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1713,6 +2083,11 @@
           <t>£1,644.52</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1728,6 +2103,11 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>£1,851.77</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
@@ -1742,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1761,6 +2141,11 @@
           <t>sale_price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1778,6 +2163,11 @@
           <t>£386.25</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1791,6 +2181,11 @@
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1808,6 +2203,11 @@
           <t>£115.65</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1825,6 +2225,11 @@
           <t>£645.81</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1842,6 +2247,11 @@
           <t>£195.29</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1859,6 +2269,11 @@
           <t>£645.81</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1876,6 +2291,11 @@
           <t>£393.42</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1893,6 +2313,11 @@
           <t>£693.89</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1910,6 +2335,11 @@
           <t>£457.26</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1927,6 +2357,11 @@
           <t>£849.63</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1944,6 +2379,11 @@
           <t>£732.58</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1961,6 +2401,11 @@
           <t>£998.44</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1978,6 +2423,11 @@
           <t>£207.74</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1995,6 +2445,11 @@
           <t>£507.01</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2012,6 +2467,11 @@
           <t>£420.65</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2029,6 +2489,11 @@
           <t>£849.63</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2046,6 +2511,11 @@
           <t>£749.80</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2063,6 +2533,11 @@
           <t>£1,309.91</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2080,6 +2555,11 @@
           <t>£609.10</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2093,6 +2573,11 @@
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2110,6 +2595,11 @@
           <t>£610.83</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2123,6 +2613,11 @@
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2140,6 +2635,11 @@
           <t>£422.36</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2153,6 +2653,11 @@
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2170,6 +2675,11 @@
           <t>£674.86</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2183,6 +2693,11 @@
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2200,6 +2715,11 @@
           <t>£854.82</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2217,6 +2737,11 @@
           <t>£998.44</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2234,6 +2759,11 @@
           <t>£646.94</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2251,6 +2781,11 @@
           <t>£1,309.91</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2268,6 +2803,11 @@
           <t>£821.47</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2285,6 +2825,11 @@
           <t>£1,474.30</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2298,6 +2843,11 @@
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2315,6 +2865,11 @@
           <t>£693.89</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2328,6 +2883,11 @@
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2345,6 +2905,11 @@
           <t>£849.63</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2362,6 +2927,11 @@
           <t>£998.44</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2379,6 +2949,11 @@
           <t>£1,152.45</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2396,6 +2971,11 @@
           <t>£1,309.91</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2413,6 +2993,11 @@
           <t>£722.01</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2430,6 +3015,11 @@
           <t>£1,631.77</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2443,6 +3033,11 @@
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2456,6 +3051,11 @@
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2473,6 +3073,11 @@
           <t>£418.46</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2490,6 +3095,11 @@
           <t>£759.65</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2503,6 +3113,11 @@
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2520,6 +3135,11 @@
           <t>£998.44</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2537,6 +3157,11 @@
           <t>£939.61</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2550,6 +3175,11 @@
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2567,6 +3197,11 @@
           <t>£1,138.60</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2580,6 +3215,11 @@
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2597,6 +3237,11 @@
           <t>£1,396.43</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2614,6 +3259,11 @@
           <t>£1,134.87</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2631,6 +3281,11 @@
           <t>£1,662.91</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2648,6 +3303,11 @@
           <t>£1,152.45</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2661,6 +3321,11 @@
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2678,6 +3343,11 @@
           <t>£1,631.77</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2695,6 +3365,11 @@
           <t>£1,256.33</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2712,6 +3387,11 @@
           <t>£1,780.58</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2729,6 +3409,11 @@
           <t>£1,415.14</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2746,6 +3431,11 @@
           <t>£2,256.44</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2763,6 +3453,11 @@
           <t>£847.81</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2780,6 +3475,11 @@
           <t>£1,168.89</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2797,6 +3497,11 @@
           <t>£1,699.37</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2814,6 +3519,11 @@
           <t>£1,902.60</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2831,6 +3541,11 @@
           <t>£580.78</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2848,6 +3563,11 @@
           <t>£517.55</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2865,6 +3585,11 @@
           <t>£556.44</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2882,6 +3607,11 @@
           <t>£897.82</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2899,6 +3629,11 @@
           <t>£693.66</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2916,6 +3651,11 @@
           <t>£777.88</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2933,6 +3673,11 @@
           <t>£461.49</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2950,6 +3695,11 @@
           <t>£405.22</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2967,6 +3717,11 @@
           <t>£496.73</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2984,6 +3739,11 @@
           <t>£370.65</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3001,6 +3761,11 @@
           <t>£541.02</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3018,6 +3783,11 @@
           <t>£450.99</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3035,6 +3805,11 @@
           <t>£291.59</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3052,6 +3827,11 @@
           <t>£555.62</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3069,6 +3849,11 @@
           <t>£457.04</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3086,6 +3871,11 @@
           <t>£514.73</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3103,6 +3893,11 @@
           <t>£493.72</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3118,6 +3913,11 @@
       <c r="C84" t="inlineStr">
         <is>
           <t>£410.57</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3149,6 +3949,759 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£ 115.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£ 92.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£ 148.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£ 354.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£ 414.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£ 700.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£ 185.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£ 395.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£ 365.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£ 790.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£ 724.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£ 245.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£ 210.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£ 350.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£ 400.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£ 424.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£ 484.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£ 604.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£ 784.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£ 364.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£ 404.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£ 414.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£ 470.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£ 535.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£ 484.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£ 540.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£ 490.00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£ 458.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£ 390.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£ 425.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£ 616.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£ 524.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£ 776.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£ 952.00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£ 844.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£ 1,144.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£ 714.00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£ 680.00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£ 950.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£ 799.00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£ 1,520.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£ 1,390.00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£ 2,100.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£ 1,900.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
@@ -3163,7 +4716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3182,6 +4735,11 @@
           <t>sale_price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3199,6 +4757,11 @@
           <t>£65.38</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3216,6 +4779,11 @@
           <t>£85.38</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3233,6 +4801,11 @@
           <t>£109.68</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3250,6 +4823,11 @@
           <t>£139.62</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3267,6 +4845,11 @@
           <t>£223.06</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3284,6 +4867,11 @@
           <t>£239.21</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3301,6 +4889,11 @@
           <t>£251.31</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3318,6 +4911,11 @@
           <t>£304.93</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3335,6 +4933,11 @@
           <t>£307.68</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3352,6 +4955,11 @@
           <t>£309.07</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3369,6 +4977,11 @@
           <t>£338.56</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3386,6 +4999,11 @@
           <t>£349.55</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3403,6 +5021,11 @@
           <t>£362.23</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3420,6 +5043,11 @@
           <t>£399.42</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3437,6 +5065,11 @@
           <t>£425.36</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3454,6 +5087,11 @@
           <t>£440.71</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3471,6 +5109,11 @@
           <t>£494.12</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3488,6 +5131,11 @@
           <t>£494.12</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3505,6 +5153,11 @@
           <t>£568.58</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3522,6 +5175,11 @@
           <t>£627.43</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3539,6 +5197,11 @@
           <t>£702.17</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3556,6 +5219,11 @@
           <t>£708.75</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3573,6 +5241,11 @@
           <t>£780.33</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3588,6 +5261,11 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>£829.22</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
@@ -3602,7 +5280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3621,6 +5299,11 @@
           <t>sale_price</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3638,6 +5321,11 @@
           <t>£476.03</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3655,6 +5343,11 @@
           <t>£412.00</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3672,6 +5365,11 @@
           <t>£298.00</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3689,6 +5387,11 @@
           <t>£376.80</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3706,6 +5409,11 @@
           <t>£337.00</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3723,6 +5431,11 @@
           <t>£303.00</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3740,6 +5453,11 @@
           <t>£381.00</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3757,6 +5475,11 @@
           <t>£251.00</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3774,6 +5497,11 @@
           <t>£354.00</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3791,6 +5519,11 @@
           <t>£743.00</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3808,6 +5541,11 @@
           <t>£197.00</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3825,6 +5563,11 @@
           <t>£674.00</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3842,6 +5585,11 @@
           <t>£381.00</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3859,6 +5607,11 @@
           <t>£303.00</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3876,6 +5629,11 @@
           <t>£691.00</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3893,6 +5651,11 @@
           <t>£314.00</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3908,6 +5671,11 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>£318.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,820 +430,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regular_price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sale_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date_scraped</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£480.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£216.30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£113.28</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£188.94</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£382.07</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£442.36</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£711.85</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£201.57</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£410.82</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£727.23</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£282.29</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£357.92</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£410.93</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£391.49</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£447.74</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£526.53</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£630.21</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£798.41</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.06</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£444.71</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£480.15</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£500.21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£540.50</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£701.67</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£406.45</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£501.19</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£538.19</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£672.95</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£872.04</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£1,097.36</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£483.65</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£756.12</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£1,219.98</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£1,366.54</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£818.47</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1293,7 +482,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1315,7 +504,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1337,7 +526,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1359,7 +548,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1381,7 +570,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1403,7 +592,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1425,7 +614,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1447,7 +636,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1469,7 +658,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1491,7 +680,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1513,7 +702,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1535,7 +724,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1557,7 +746,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1579,7 +768,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1601,7 +790,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1623,7 +812,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1645,7 +834,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1667,7 +856,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1689,7 +878,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1711,7 +900,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1733,7 +922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1755,7 +944,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1777,7 +966,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1799,7 +988,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1010,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1032,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1054,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1076,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1098,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1120,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1142,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1164,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1186,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2019,7 +1208,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2041,7 +1230,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2063,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2085,7 +1274,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2107,7 +1296,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2165,7 +1354,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2183,7 +1372,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2205,7 +1394,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2227,7 +1416,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2249,7 +1438,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2271,7 +1460,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2293,7 +1482,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2315,7 +1504,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2337,7 +1526,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2359,7 +1548,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2381,7 +1570,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2403,7 +1592,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2425,7 +1614,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2447,7 +1636,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2469,7 +1658,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2491,7 +1680,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2513,7 +1702,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2535,7 +1724,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2557,7 +1746,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2575,7 +1764,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2597,7 +1786,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2615,7 +1804,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2637,7 +1826,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2655,7 +1844,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2677,7 +1866,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2695,7 +1884,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2717,7 +1906,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2739,7 +1928,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2761,7 +1950,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2783,7 +1972,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2805,7 +1994,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2016,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2034,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2056,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2074,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2096,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2118,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2140,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2162,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2184,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3017,7 +2206,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3035,7 +2224,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3053,7 +2242,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3075,7 +2264,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3097,7 +2286,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3115,7 +2304,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3137,7 +2326,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3159,7 +2348,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3177,7 +2366,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3199,7 +2388,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3217,7 +2406,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3239,7 +2428,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3261,7 +2450,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3283,7 +2472,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3305,7 +2494,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3323,7 +2512,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3345,7 +2534,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3367,7 +2556,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3389,7 +2578,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3411,7 +2600,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3433,7 +2622,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3455,7 +2644,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3477,7 +2666,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3499,7 +2688,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3521,7 +2710,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3543,7 +2732,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3565,7 +2754,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3587,7 +2776,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3609,7 +2798,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3631,7 +2820,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3653,7 +2842,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3675,7 +2864,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3697,7 +2886,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3719,7 +2908,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3741,7 +2930,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3763,7 +2952,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3785,7 +2974,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3807,7 +2996,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3018,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3040,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3062,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3084,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3106,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3965,17 +3154,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£ 115.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>£ 92.00</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -3987,17 +3172,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>£ 148.00</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4009,17 +3190,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>£ 354.00</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4031,17 +3208,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>£ 414.00</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4053,17 +3226,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>£ 700.00</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4075,17 +3244,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£ 185.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>£ 165.00</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4097,17 +3262,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£ 395.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>£ 365.00</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4119,17 +3280,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£ 790.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>£ 724.00</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4141,17 +3298,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£ 245.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>£ 210.00</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4163,17 +3316,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>£ 350.00</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4185,17 +3334,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>£ 400.00</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4207,17 +3352,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
           <t>£ 380.00</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4229,17 +3370,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>£ 424.00</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4251,17 +3388,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>£ 484.00</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4273,17 +3406,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£ 660.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>£ 604.00</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4295,17 +3424,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>£ 784.00</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4317,17 +3442,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>£ 364.00</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4339,17 +3460,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
           <t>£ 404.00</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4361,17 +3478,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>£ 414.00</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4383,17 +3496,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>£ 470.00</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4405,17 +3514,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£ 535.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>£ 484.00</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4427,17 +3532,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£ 540.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>£ 490.00</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4449,17 +3550,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£ 458.00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>£ 390.00</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4471,17 +3568,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>£ 425.00</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4493,17 +3586,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£ 616.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
           <t>£ 524.00</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4515,17 +3604,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£ 776.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
           <t>£ 660.00</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4537,17 +3622,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£ 952.00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>£ 844.00</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4559,17 +3640,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£ 1,250.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
           <t>£ 1,144.00</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4581,17 +3658,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
           <t>£ 454.00</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4603,17 +3676,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
           <t>£ 714.00</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4625,17 +3694,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
           <t>£ 680.00</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4647,17 +3712,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£ 950.00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
           <t>£ 799.00</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4669,17 +3730,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£ 1,520.00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>£ 1,390.00</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4691,17 +3748,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£ 2,100.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>£ 1,900.00</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4759,7 +3812,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4781,7 +3834,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4803,95 +3856,91 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600x600mm Rooflight</t>
+          <t>600x900mm Rooflight</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£279.23</t>
+          <t>£318.66</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£139.62</t>
+          <t>£223.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>600x900mm Rooflight</t>
+          <t>600x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£318.66</t>
+          <t>£398.68</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£223.06</t>
+          <t>£239.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>600x1200mm Rooflight</t>
+          <t>800x800mm Rooflight</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£398.68</t>
+          <t>£359.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£239.21</t>
+          <t>£251.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>800x800mm Rooflight</t>
+          <t>600x600mm Rooflight</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£359.02</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£251.31</t>
-        </is>
-      </c>
+          <t>£279.23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4913,7 +3962,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4935,7 +3984,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4006,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5001,7 +4050,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5023,7 +4072,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5045,7 +4094,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5067,7 +4116,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5089,14 +4138,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1200x2000mm Rooflight</t>
+          <t>1200x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5111,117 +4160,117 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1200x1200mm Rooflight</t>
+          <t>1000x2000mm Rooflight</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£705.89</t>
+          <t>£947.64</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£494.12</t>
+          <t>£568.58</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1000x2000mm Rooflight</t>
+          <t>1500x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£947.64</t>
+          <t>£1,045.71</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£568.58</t>
+          <t>£627.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1500x1500mm Rooflight</t>
+          <t>1000x2500mm Rooflight</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£1,045.71</t>
+          <t>£1,170.29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£627.43</t>
+          <t>£702.17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1000x2500mm Rooflight</t>
+          <t>1200x1800mm Rooflight</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£1,170.29</t>
+          <t>£1,012.51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£702.17</t>
+          <t>£708.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1200x1800mm Rooflight</t>
+          <t>1200x2000mm Rooflight</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1,012.51</t>
+          <t>£1,114.75</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£708.75</t>
+          <t>£780.33</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5243,7 +4292,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5265,7 +4314,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5318,12 +4367,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£476.03</t>
+          <t>£457.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5345,7 +4394,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5367,7 +4416,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5389,7 +4438,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5411,7 +4460,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5433,7 +4482,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5455,7 +4504,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5477,7 +4526,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5499,7 +4548,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5521,7 +4570,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5543,51 +4592,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£674.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£674.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5609,7 +4658,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5631,7 +4680,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5653,7 +4702,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>
@@ -5675,7 +4724,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,9 +430,820 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£480.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£113.28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£188.94</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£382.07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£442.36</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£711.85</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£201.57</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£410.82</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£727.23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£282.29</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£357.92</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£410.93</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£391.49</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£447.74</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£526.53</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£630.21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£798.41</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£444.71</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£480.15</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£500.21</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£540.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£701.67</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£406.45</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£501.19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£538.19</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£672.95</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£872.04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£1,097.36</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£483.65</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£756.12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£1,219.98</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£1,366.54</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£818.47</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -482,7 +1293,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -504,7 +1315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -526,7 +1337,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -548,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -570,7 +1381,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -592,7 +1403,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -614,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -636,7 +1447,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -658,7 +1469,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -680,7 +1491,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -702,7 +1513,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -724,7 +1535,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -746,7 +1557,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -768,7 +1579,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -790,7 +1601,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -812,7 +1623,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -834,7 +1645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -856,7 +1667,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -878,7 +1689,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -900,7 +1711,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -922,7 +1733,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -944,7 +1755,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -966,7 +1777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -988,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1821,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1843,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1887,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1909,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1931,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1975,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1208,7 +2019,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1230,7 +2041,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1252,7 +2063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1274,7 +2085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1296,7 +2107,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1354,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1372,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1394,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1416,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1438,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1460,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1482,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1504,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1526,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1548,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1570,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1592,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1614,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1636,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1658,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1680,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1702,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1724,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1746,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1764,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1786,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1804,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1826,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1844,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1866,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1884,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1906,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1928,7 +2739,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1950,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1972,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2929,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2951,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2973,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2995,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2206,7 +3017,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2224,7 +3035,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2242,7 +3053,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2264,7 +3075,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2286,7 +3097,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2304,7 +3115,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2326,7 +3137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2348,7 +3159,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2366,7 +3177,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2388,7 +3199,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2406,7 +3217,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2428,7 +3239,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2450,7 +3261,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2472,7 +3283,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2494,7 +3305,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2512,7 +3323,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2534,7 +3345,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2556,7 +3367,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2578,7 +3389,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2600,7 +3411,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2622,7 +3433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2644,7 +3455,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2666,7 +3477,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2688,7 +3499,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2710,7 +3521,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2732,7 +3543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2754,7 +3565,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2776,7 +3587,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2798,7 +3609,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2820,7 +3631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2842,7 +3653,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2864,7 +3675,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2886,7 +3697,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2908,7 +3719,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2930,7 +3741,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2952,7 +3763,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2974,7 +3785,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3829,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3851,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3873,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3895,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3917,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3154,13 +3965,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>£ 115.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>£ 92.00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3172,13 +3987,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>£ 148.00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3190,13 +4009,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>£ 354.00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3208,13 +4031,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>£ 414.00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3226,13 +4053,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>£ 700.00</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3244,13 +4075,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>£ 185.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>£ 165.00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3262,13 +4097,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>£ 395.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>£ 365.00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3280,13 +4119,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>£ 790.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>£ 724.00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3298,13 +4141,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>£ 245.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>£ 210.00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3316,13 +4163,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>£ 350.00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3334,13 +4185,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>£ 400.00</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3352,13 +4207,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>£ 380.00</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3370,13 +4229,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>£ 424.00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3388,13 +4251,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>£ 484.00</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3406,13 +4273,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>£ 604.00</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3424,13 +4295,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>£ 784.00</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3442,13 +4317,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>£ 364.00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3460,13 +4339,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>£ 404.00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3478,13 +4361,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>£ 414.00</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3496,13 +4383,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>£ 470.00</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3514,13 +4405,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>£ 535.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>£ 484.00</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3532,13 +4427,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>£ 540.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>£ 490.00</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3550,13 +4449,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>£ 458.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>£ 390.00</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3568,13 +4471,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>£ 425.00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3586,13 +4493,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>£ 616.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>£ 524.00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3604,13 +4515,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>£ 776.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>£ 660.00</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3622,13 +4537,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>£ 952.00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>£ 844.00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3640,13 +4559,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>£ 1,144.00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3658,13 +4581,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>£ 454.00</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3676,13 +4603,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>£ 714.00</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3694,13 +4625,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>£ 680.00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3712,13 +4647,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>£ 950.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>£ 799.00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3730,13 +4669,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>£ 1,520.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>£ 1,390.00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3748,13 +4691,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>£ 2,100.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>£ 1,900.00</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3807,12 +4754,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£65.38</t>
+          <t>£84.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3829,12 +4776,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£85.38</t>
+          <t>£119.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3851,96 +4798,100 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£109.68</t>
+          <t>£153.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600x900mm Rooflight</t>
+          <t>600x600mm Rooflight</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£318.66</t>
+          <t>£279.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£223.06</t>
+          <t>£195.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>600x1200mm Rooflight</t>
+          <t>600x900mm Rooflight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£398.68</t>
+          <t>£318.66</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£239.21</t>
+          <t>£223.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>800x800mm Rooflight</t>
+          <t>600x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£359.02</t>
+          <t>£398.68</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£251.31</t>
+          <t>£239.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>600x600mm Rooflight</t>
+          <t>800x800mm Rooflight</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£279.23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>£359.02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£251.31</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3962,7 +4913,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -3984,7 +4935,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4957,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4979,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4050,7 +5001,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4072,7 +5023,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4094,7 +5045,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4116,7 +5067,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4138,7 +5089,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4160,7 +5111,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4182,7 +5133,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4204,7 +5155,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4226,7 +5177,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4248,7 +5199,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4270,51 +5221,51 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1800x1800mm Rooflight</t>
+          <t>1000x3000mm Rooflight</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£1,114.75</t>
+          <t>£1,382.03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£780.33</t>
+          <t>£829.22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1000x3000mm Rooflight</t>
+          <t>1800x1800mm Rooflight</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£1,382.03</t>
+          <t>£1,114.75</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>£829.22</t>
+          <t>£1,016.22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4372,7 +5323,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4394,7 +5345,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4416,7 +5367,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4438,7 +5389,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4460,7 +5411,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4482,7 +5433,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4504,7 +5455,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4526,7 +5477,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4548,7 +5499,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4570,7 +5521,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4592,51 +5543,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£674.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£674.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4658,51 +5609,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1500mm x 1500mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1000mm</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£1,250.00</t>
+          <t>£800.00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£691.00</t>
+          <t>£314.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1000mm</t>
+          <t>Flat Rooflights &amp; Skylights 1500mm x 1500mm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£800.00</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£314.00</t>
+          <t>£691.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -4724,7 +5675,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,820 +430,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regular_price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sale_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date_scraped</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£480.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£216.30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£113.28</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£188.94</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£382.07</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£442.36</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£711.85</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£201.57</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£410.82</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£727.23</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£282.29</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£357.92</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£410.93</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£391.49</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£447.74</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£526.53</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£630.21</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£798.41</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.06</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£444.71</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£480.15</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£500.21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£540.50</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£701.67</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£406.45</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£501.19</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£538.19</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£672.95</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£872.04</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£1,097.36</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£483.65</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£756.12</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£1,219.98</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£1,366.54</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£818.47</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1254,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,832 +471,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£216.30</t>
+          <t>£3,037.32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£102.07</t>
+          <t>£1,851.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£172.36</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£347.24</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£403.58</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£646.58</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£183.35</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£371.27</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£661.78</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£257.36</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£327.14</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£372.78</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£357.65</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£407.32</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£477.51</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£571.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£725.04</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£362.37</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.05</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£403.39</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£435.76</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£454.31</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£490.40</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£637.25</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£369.34</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£456.80</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£491.12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£612.24</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£792.43</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£1,104.29</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£686.56</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£1,108.85</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£1,369.18</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£821.76</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£2,079.00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£1,164.84</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>£2,585.00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>£1,644.52</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>£3,037.32</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>£1,851.77</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2165,7 +566,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2183,7 +584,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2205,7 +606,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2227,7 +628,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2249,7 +650,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2271,7 +672,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2293,7 +694,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2315,7 +716,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2337,7 +738,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2359,7 +760,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2381,7 +782,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2403,7 +804,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2425,7 +826,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2447,7 +848,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2469,7 +870,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2491,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2513,7 +914,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2535,7 +936,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2557,7 +958,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2575,7 +976,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2597,7 +998,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2615,7 +1016,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2637,7 +1038,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2655,7 +1056,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2677,7 +1078,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2695,7 +1096,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2717,7 +1118,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2739,7 +1140,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2761,7 +1162,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2783,7 +1184,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2805,7 +1206,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2827,7 +1228,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2845,7 +1246,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2867,7 +1268,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2885,7 +1286,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2907,7 +1308,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2929,7 +1330,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2951,7 +1352,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2973,7 +1374,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2995,7 +1396,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3017,7 +1418,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3035,7 +1436,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3053,7 +1454,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3075,7 +1476,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3097,7 +1498,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3115,7 +1516,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3137,7 +1538,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3159,7 +1560,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3177,7 +1578,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3199,7 +1600,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3217,7 +1618,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3239,7 +1640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3261,7 +1662,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3283,7 +1684,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3305,7 +1706,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3323,7 +1724,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3345,7 +1746,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3362,12 +1763,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>£1,256.33</t>
+          <t>£867.71</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3389,7 +1790,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3411,7 +1812,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3433,7 +1834,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3450,12 +1851,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>£847.81</t>
+          <t>£901.33</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3477,7 +1878,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3499,7 +1900,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3521,7 +1922,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3543,7 +1944,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3565,7 +1966,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3587,7 +1988,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3609,7 +2010,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3631,7 +2032,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3653,7 +2054,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3675,7 +2076,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3697,7 +2098,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3719,7 +2120,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3741,7 +2142,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3763,7 +2164,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3785,7 +2186,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3807,7 +2208,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3829,7 +2230,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3851,7 +2252,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3873,7 +2274,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3895,7 +2296,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3917,7 +2318,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -3932,780 +2333,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regular_price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sale_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date_scraped</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 300 x 300 mm</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£ 115.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>£ 92.00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 400 mm</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£ 148.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£ 354.00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£ 414.00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£ 700.00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 500 x 500 mm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£ 185.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£ 395.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£ 365.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£ 790.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£ 724.00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 600 mm</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£ 245.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£ 210.00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 900 mm</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£ 350.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£ 400.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£ 424.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£ 484.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£ 660.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£ 604.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£ 784.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 800 mm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£ 364.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£ 404.00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£ 414.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£ 470.00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£ 535.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£ 484.00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£ 540.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£ 490.00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£ 458.00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£ 390.00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£ 425.00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£ 616.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£ 524.00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£ 776.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£ 660.00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£ 952.00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£ 844.00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£ 1,250.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£ 1,144.00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1200 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1200 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£ 714.00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1200 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£ 680.00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£ 950.00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£ 799.00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1500 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£ 1,520.00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£ 1,390.00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£ 2,100.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£ 1,900.00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4759,7 +2389,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4781,7 +2411,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4803,7 +2433,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4825,7 +2455,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4847,7 +2477,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4869,7 +2499,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4891,7 +2521,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4913,7 +2543,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4935,7 +2565,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4957,7 +2587,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -4979,7 +2609,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5001,7 +2631,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5023,7 +2653,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5045,7 +2675,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5067,7 +2697,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5089,7 +2719,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5111,7 +2741,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5133,7 +2763,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5155,7 +2785,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5177,7 +2807,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5199,7 +2829,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5221,7 +2851,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5243,7 +2873,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5265,7 +2895,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5323,7 +2953,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5345,7 +2975,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5367,7 +2997,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5389,7 +3019,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5411,7 +3041,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5433,7 +3063,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5455,7 +3085,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5477,7 +3107,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5499,7 +3129,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5521,7 +3151,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5543,7 +3173,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5565,7 +3195,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5587,7 +3217,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5609,7 +3239,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5631,7 +3261,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5653,7 +3283,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -5675,7 +3305,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,9 +430,820 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£480.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£113.28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£188.94</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£382.07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£442.36</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£711.85</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£201.57</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£410.82</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£727.23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£282.29</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£357.92</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£410.93</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£391.49</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£447.74</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£526.53</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£630.21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£798.41</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£444.71</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£480.15</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£500.21</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£540.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£701.67</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£406.45</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£501.19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£538.19</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£672.95</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£872.04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£1,097.36</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£483.65</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£756.12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£870.35</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£1,366.54</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£899.15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -443,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,44 +1282,832 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£2,585.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>£1,644.52</t>
-        </is>
-      </c>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£102.07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£172.36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£347.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£403.58</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£646.58</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£183.35</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£371.27</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£661.78</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£257.36</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£327.14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£372.78</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£357.65</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£407.32</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£477.51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£571.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£725.04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£362.37</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£403.39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£435.76</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£454.31</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£490.40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£637.25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£369.34</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£456.80</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£491.12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£612.24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£792.43</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£1,104.29</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£686.56</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£831.27</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£1,369.18</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£851.76</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£2,079.00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£1,164.84</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>£3,037.32</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>£1,851.77</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -566,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -584,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -606,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -628,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -650,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -672,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -694,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -716,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -738,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -760,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -782,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -804,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -826,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -848,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -870,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -892,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -914,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -936,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -958,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -976,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -998,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1016,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1038,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1056,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1078,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1096,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1118,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1140,7 +2739,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1162,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1184,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1206,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1228,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1246,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1268,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1286,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1308,7 +2907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1330,7 +2929,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1352,7 +2951,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1374,7 +2973,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1396,7 +2995,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1418,7 +3017,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1436,7 +3035,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1454,7 +3053,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1476,7 +3075,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1498,7 +3097,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1516,7 +3115,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1538,7 +3137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1560,7 +3159,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1578,7 +3177,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1600,7 +3199,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1618,7 +3217,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1640,7 +3239,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1662,7 +3261,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1684,7 +3283,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1706,7 +3305,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1724,7 +3323,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1746,7 +3345,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1768,7 +3367,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1790,7 +3389,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1812,7 +3411,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1834,7 +3433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1856,7 +3455,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1878,7 +3477,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1900,7 +3499,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1922,7 +3521,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1944,7 +3543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1966,7 +3565,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -1988,7 +3587,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2010,7 +3609,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2032,7 +3631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2054,7 +3653,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2076,7 +3675,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2098,7 +3697,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2120,7 +3719,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2142,7 +3741,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2164,7 +3763,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2186,7 +3785,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2208,7 +3807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2230,7 +3829,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2252,7 +3851,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2274,7 +3873,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2296,7 +3895,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2318,7 +3917,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2333,9 +3932,780 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£ 115.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£ 92.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£ 148.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£ 354.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£ 414.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£ 700.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£ 185.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£ 395.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£ 365.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£ 790.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£ 724.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£ 245.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£ 210.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£ 350.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£ 400.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£ 424.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£ 484.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£ 604.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£ 784.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£ 364.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£ 404.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£ 414.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£ 470.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£ 535.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£ 484.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£ 540.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£ 490.00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£ 458.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£ 390.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£ 425.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£ 616.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£ 524.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£ 776.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£ 952.00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£ 844.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£ 1,144.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£ 714.00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£ 680.00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£ 950.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£ 799.00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£ 1,520.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£ 1,390.00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£ 2,100.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£ 1,900.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2389,7 +4759,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2411,7 +4781,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2433,7 +4803,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2455,7 +4825,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2477,7 +4847,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2499,7 +4869,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2521,7 +4891,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2543,7 +4913,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2565,7 +4935,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2587,7 +4957,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2609,7 +4979,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2631,7 +5001,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2653,7 +5023,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2675,7 +5045,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2697,7 +5067,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2719,7 +5089,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2741,7 +5111,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2763,7 +5133,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2785,7 +5155,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2807,7 +5177,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2829,7 +5199,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2851,7 +5221,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2873,7 +5243,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2895,7 +5265,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2953,7 +5323,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2975,7 +5345,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -2997,7 +5367,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3019,7 +5389,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3041,7 +5411,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3063,7 +5433,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3085,7 +5455,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3107,7 +5477,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3129,7 +5499,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3151,7 +5521,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3173,7 +5543,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3195,7 +5565,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3217,7 +5587,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3239,7 +5609,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3261,7 +5631,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3283,7 +5653,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
@@ -3305,7 +5675,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -469,7 +469,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3932,780 +3932,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regular_price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sale_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date_scraped</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 300 x 300 mm</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£ 115.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>£ 92.00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 400 mm</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£ 148.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£ 354.00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£ 414.00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 400 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£ 700.00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 500 x 500 mm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£ 185.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£ 395.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£ 365.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£ 790.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£ 724.00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 600 mm</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£ 245.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£ 210.00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 900 mm</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£ 350.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£ 400.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£ 424.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£ 484.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£ 660.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£ 604.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 600 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£ 784.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 800 mm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£ 364.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£ 404.00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£ 414.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£ 470.00</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£ 535.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£ 484.00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 800 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£ 540.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£ 490.00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£ 458.00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£ 390.00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£ 425.00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£ 616.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£ 524.00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£ 776.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£ 660.00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£ 952.00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£ 844.00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1000 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£ 1,250.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£ 1,144.00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1200 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1200 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£ 714.00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1200 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£ 680.00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£ 950.00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£ 799.00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1500 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£ 1,520.00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£ 1,390.00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Flat Roof Triple Glazed Skylight 1500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£ 2,100.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£ 1,900.00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4716,7 +3945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4744,528 +3973,264 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rooflight 300x300mm</t>
+          <t>1000x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£130.76</t>
+          <t>£603.71</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£84.99</t>
+          <t>£362.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>400x400mm Rooflight Skylight</t>
+          <t>600x1800mm Rooflight</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£170.76</t>
+          <t>£570.60</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£119.53</t>
+          <t>£399.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>500x500mm Rooflight</t>
+          <t>800x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£219.36</t>
+          <t>£607.67</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£153.55</t>
+          <t>£425.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600x600mm Rooflight</t>
+          <t>1000x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£279.23</t>
+          <t>£734.52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£195.46</t>
+          <t>£440.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>600x900mm Rooflight</t>
+          <t>1200x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£318.66</t>
+          <t>£705.89</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£223.06</t>
+          <t>£494.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>600x1200mm Rooflight</t>
+          <t>1000x2000mm Rooflight</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£398.68</t>
+          <t>£947.64</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£239.21</t>
+          <t>£568.58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>800x800mm Rooflight</t>
+          <t>1500x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£359.02</t>
+          <t>£1,045.71</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£251.31</t>
+          <t>£627.43</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>800x1000mm Rooflight</t>
+          <t>1000x2500mm Rooflight</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£435.62</t>
+          <t>£1,170.29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£304.93</t>
+          <t>£702.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>900x900mm Rooflight</t>
+          <t>1200x1800mm Rooflight</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£439.54</t>
+          <t>£1,012.51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£307.68</t>
+          <t>£708.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1000x1000mm Rooflight</t>
+          <t>1200x2000mm Rooflight</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£515.11</t>
+          <t>£1,114.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£309.07</t>
+          <t>£780.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>600x1500mm Rooflight</t>
+          <t>1000x3000mm Rooflight</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£483.65</t>
+          <t>£1,382.03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£338.56</t>
+          <t>£829.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>800x1200mm Rooflight Skylight</t>
+          <t>1800x1800mm Rooflight</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£499.36</t>
+          <t>£1,114.75</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£349.55</t>
+          <t>£1,016.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1000x1200mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£603.71</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£362.23</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>600x1800mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£570.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£399.42</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>800x1500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£607.67</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£425.36</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1000x1500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£734.52</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£440.71</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1200x1200mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£705.89</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£494.12</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1000x2000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£947.64</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£568.58</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1500x1500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£1,045.71</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£627.43</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1000x2500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£1,170.29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£702.17</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1200x1800mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£1,012.51</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£708.75</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1200x2000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£1,114.75</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£780.33</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1000x3000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£1,382.03</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£829.22</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1800x1800mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£1,114.75</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£1,016.22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5323,7 +4288,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5345,7 +4310,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5367,7 +4332,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5389,7 +4354,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5411,7 +4376,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5433,7 +4398,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5455,7 +4420,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5477,7 +4442,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5499,7 +4464,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5521,7 +4486,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5543,7 +4508,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5565,7 +4530,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5587,7 +4552,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5609,7 +4574,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5631,7 +4596,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5653,7 +4618,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -5675,7 +4640,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -469,7 +469,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -3932,9 +3932,802 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£ 115.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£ 85.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£ 130.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£ 354.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£ 360.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£ 700.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£ 185.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£ 395.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£ 320.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£ 790.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£ 580.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£ 245.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£ 210.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£ 350.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£ 400.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£ 310.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£ 360.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£ 455.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£ 604.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£ 580.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£ 364.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£ 404.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£ 410.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£ 535.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£ 484.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£ 540.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£ 490.00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 900 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£ 425.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£ 360.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£ 458.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£ 370.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£ 425.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£ 616.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£ 490.00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£ 776.00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£ 610.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£ 952.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£ 844.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£ 910.00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£ 650.00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£ 620.00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£ 950.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£ 720.00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£ 1,520.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£ 1,390.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£ 2,100.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£ 1,900.00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3945,7 +4738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3973,264 +4766,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1000x1200mm Rooflight</t>
+          <t>Rooflight 300x300mm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£603.71</t>
+          <t>£130.76</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£362.23</t>
+          <t>£84.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>600x1800mm Rooflight</t>
+          <t>400x400mm Rooflight Skylight</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£570.60</t>
+          <t>£170.76</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£399.42</t>
+          <t>£119.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>800x1500mm Rooflight</t>
+          <t>500x500mm Rooflight</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£607.67</t>
+          <t>£219.36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£425.36</t>
+          <t>£153.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1000x1500mm Rooflight</t>
+          <t>600x600mm Rooflight</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£734.52</t>
+          <t>£279.23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£440.71</t>
+          <t>£195.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1200x1200mm Rooflight</t>
+          <t>600x900mm Rooflight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£705.89</t>
+          <t>£318.66</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£494.12</t>
+          <t>£223.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1000x2000mm Rooflight</t>
+          <t>600x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£947.64</t>
+          <t>£398.68</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£568.58</t>
+          <t>£239.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1500x1500mm Rooflight</t>
+          <t>800x800mm Rooflight</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£1,045.71</t>
+          <t>£359.02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£627.43</t>
+          <t>£251.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1000x2500mm Rooflight</t>
+          <t>800x1000mm Rooflight</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£1,170.29</t>
+          <t>£435.62</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£702.17</t>
+          <t>£304.93</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1200x1800mm Rooflight</t>
+          <t>900x900mm Rooflight</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£1,012.51</t>
+          <t>£439.54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£708.75</t>
+          <t>£307.68</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1200x2000mm Rooflight</t>
+          <t>1000x1000mm Rooflight</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£1,114.75</t>
+          <t>£515.11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£780.33</t>
+          <t>£309.07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1000x3000mm Rooflight</t>
+          <t>600x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£1,382.03</t>
+          <t>£483.65</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£829.22</t>
+          <t>£338.56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>800x1200mm Rooflight Skylight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£499.36</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£349.55</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1000x1200mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£603.71</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£362.23</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>600x1800mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£570.60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£399.42</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>800x1500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£607.67</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£425.36</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1000x1500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£734.52</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£440.71</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1200x1200mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£705.89</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£494.12</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1000x2000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£947.64</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£568.58</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1500x1500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£1,045.71</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£627.43</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1000x2500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£1,170.29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£702.17</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1200x1800mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£1,012.51</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£708.75</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1200x2000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£1,114.75</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£780.33</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1000x3000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£1,382.03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£829.22</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>1800x1800mm Rooflight</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>£1,114.75</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>£1,016.22</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4288,7 +5345,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4310,7 +5367,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4332,7 +5389,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4354,7 +5411,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4376,7 +5433,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4398,7 +5455,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4420,7 +5477,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4442,7 +5499,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4464,7 +5521,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4486,7 +5543,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4508,7 +5565,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4530,7 +5587,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +5609,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4574,7 +5631,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4596,7 +5653,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4618,7 +5675,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
@@ -4640,7 +5697,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -469,7 +469,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3965,17 +3965,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£ 115.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>£ 85.00</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -3987,17 +3983,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>£ 130.00</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4009,17 +4001,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>£ 354.00</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4031,17 +4019,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>£ 360.00</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4053,17 +4037,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>£ 700.00</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4075,17 +4055,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£ 185.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>£ 165.00</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4097,17 +4073,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£ 395.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>£ 320.00</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4119,17 +4091,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£ 790.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>£ 580.00</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4141,17 +4109,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£ 245.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>£ 210.00</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4163,17 +4127,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>£ 350.00</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4185,17 +4145,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>£ 400.00</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4207,17 +4163,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
           <t>£ 310.00</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4229,17 +4181,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>£ 360.00</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4251,17 +4199,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>£ 455.00</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4217,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£ 660.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>£ 604.00</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4295,17 +4235,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>£ 580.00</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4253,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>£ 364.00</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4339,17 +4271,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
           <t>£ 404.00</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4361,17 +4289,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>£ 380.00</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4383,17 +4307,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>£ 410.00</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4405,17 +4325,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£ 535.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>£ 484.00</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4427,17 +4343,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£ 540.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>£ 490.00</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4449,17 +4361,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£ 425.00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>£ 360.00</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4471,17 +4379,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£ 458.00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>£ 370.00</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4493,17 +4397,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
           <t>£ 425.00</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4515,17 +4415,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£ 616.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
           <t>£ 490.00</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4537,17 +4433,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£ 776.00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>£ 610.00</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4559,17 +4451,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£ 952.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
           <t>£ 844.00</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4581,17 +4469,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£ 1,250.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
           <t>£ 910.00</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4603,17 +4487,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
           <t>£ 454.00</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4625,17 +4505,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
           <t>£ 650.00</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4647,17 +4523,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
           <t>£ 620.00</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4669,17 +4541,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£ 950.00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>£ 720.00</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4691,17 +4559,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£ 1,520.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>£ 1,390.00</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4713,17 +4577,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£ 2,100.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
           <t>£ 1,900.00</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4641,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4663,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4685,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4707,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4729,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4751,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4773,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4795,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4817,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4839,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5001,7 +4861,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5023,7 +4883,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5045,7 +4905,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5067,7 +4927,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5089,7 +4949,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5111,7 +4971,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5133,7 +4993,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5015,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5037,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5059,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5081,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5103,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5125,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5147,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5205,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5227,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5249,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5293,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5315,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5337,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5359,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5381,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5403,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5425,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5447,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5469,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5491,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5513,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5535,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5557,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,820 +430,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regular_price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sale_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date_scraped</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£480.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£216.30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£113.28</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£188.94</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£382.07</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£442.36</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£711.85</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£201.57</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£410.82</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£727.23</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£282.29</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£357.92</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£410.93</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£391.49</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£447.74</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£526.53</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£630.21</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£798.41</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.06</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£444.71</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£480.15</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£500.21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£540.50</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£701.67</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£406.45</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£501.19</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£538.19</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£672.95</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£872.04</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£1,097.36</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£483.65</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£756.12</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£870.35</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£1,366.54</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£899.15</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1293,7 +482,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1315,7 +504,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1337,7 +526,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1359,7 +548,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1381,7 +570,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1403,7 +592,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1425,7 +614,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1447,7 +636,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1469,7 +658,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1491,7 +680,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1513,7 +702,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1535,7 +724,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1557,7 +746,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1579,7 +768,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1601,7 +790,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1623,7 +812,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1645,7 +834,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1667,7 +856,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1689,7 +878,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1711,7 +900,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1733,7 +922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1755,7 +944,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1777,7 +966,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1799,7 +988,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1010,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1032,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1054,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1076,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1098,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1120,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1142,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1164,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1186,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2019,7 +1208,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2041,7 +1230,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2063,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2085,7 +1274,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2107,7 +1296,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2122,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,7 +1354,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2183,7 +1372,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2205,7 +1394,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2227,7 +1416,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2249,7 +1438,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2271,7 +1460,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2293,7 +1482,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +1504,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2337,7 +1526,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2359,7 +1548,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2381,7 +1570,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2403,7 +1592,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2425,7 +1614,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2447,7 +1636,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2469,7 +1658,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2491,7 +1680,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2513,7 +1702,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2535,7 +1724,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2557,7 +1746,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2575,7 +1764,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2597,7 +1786,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2615,7 +1804,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2637,7 +1826,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2655,7 +1844,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2677,7 +1866,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2695,7 +1884,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2717,7 +1906,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2734,12 +1923,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£969.36</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2761,7 +1950,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2783,7 +1972,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2805,7 +1994,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2016,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2034,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2056,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2074,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -2907,1017 +2096,249 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£577.83</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£405.22</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
+          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£1,452.30</t>
+          <t>£714.82</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>£1,152.45</t>
+          <t>£496.73</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£1,648.00</t>
+          <t>£513.97</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>£1,309.91</t>
+          <t>£370.65</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£1,011.46</t>
+          <t>£715.85</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>£722.01</t>
+          <t>£541.02</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£2,039.40</t>
+          <t>£630.36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£1,631.77</t>
+          <t>£450.99</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£802.04</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>£398.61</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>£291.59</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£968.90</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>£779.71</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>£555.62</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£733.36</t>
+          <t>£754.99</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>£418.46</t>
+          <t>£457.04</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
+          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£968.20</t>
+          <t>£695.25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>£759.65</t>
+          <t>£514.73</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£866.56</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>£633.45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>£493.72</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£577.83</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£410.57</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>£1,184.50</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>£939.61</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>£1,134.65</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>£1,431.70</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>£1,138.60</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>£1,521.76</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>£1,751.00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>£1,396.43</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>£1,850.91</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>£1,134.87</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>£2,080.60</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>£1,662.91</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>£1,452.30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>£1,152.45</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>£1,092.38</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>£2,039.40</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>£1,631.77</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>£1,784.99</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>£867.71</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>£2,224.80</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>£1,780.58</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>£2,058.97</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>£1,415.14</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>£2,811.90</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>£2,256.44</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>£1,646.97</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>£901.33</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>£2,185.66</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>£1,168.89</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>£2,729.50</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>£1,699.37</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>£3,189.91</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>£1,902.60</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>£746.75</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>£580.78</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>£807.52</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>£517.55</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>£872.41</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>£556.44</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>£1,264.84</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>£897.82</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>£1,028.97</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>£693.66</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>£1,042.36</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>£777.88</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>£609.76</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>£461.49</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>£577.83</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>£405.22</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>£714.82</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>£496.73</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>£513.97</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>£370.65</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>£715.85</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>£541.02</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>£630.36</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>£450.99</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>£398.61</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>£291.59</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>£779.71</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>£555.62</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>£754.99</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>£457.04</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>£695.25</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>£514.73</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>£633.45</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>£493.72</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>£577.83</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>£410.57</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -3971,7 +2392,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -3989,7 +2410,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4007,7 +2428,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4025,7 +2446,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4043,7 +2464,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4061,7 +2482,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4079,7 +2500,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4097,7 +2518,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4115,7 +2536,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4133,7 +2554,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4151,7 +2572,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4169,7 +2590,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4187,7 +2608,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4205,7 +2626,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4223,7 +2644,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4241,7 +2662,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4259,7 +2680,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4277,7 +2698,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4295,7 +2716,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4313,7 +2734,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4331,7 +2752,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4349,7 +2770,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4367,7 +2788,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4385,7 +2806,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4403,7 +2824,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4421,7 +2842,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4439,7 +2860,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +2878,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4475,7 +2896,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4493,7 +2914,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4511,7 +2932,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4529,7 +2950,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4547,7 +2968,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4565,7 +2986,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4583,7 +3004,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4626,352 +3047,352 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rooflight 300x300mm</t>
+          <t>600x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£130.76</t>
+          <t>£398.68</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£84.99</t>
+          <t>£239.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>400x400mm Rooflight Skylight</t>
+          <t>800x1200mm Rooflight Skylight</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£170.76</t>
+          <t>£499.36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£119.53</t>
+          <t>£349.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>500x500mm Rooflight</t>
+          <t>1000x1000mm Rooflight</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£219.36</t>
+          <t>£515.11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£153.55</t>
+          <t>£309.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600x600mm Rooflight</t>
+          <t>1000x2000mm Rooflight</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£279.23</t>
+          <t>£947.64</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£195.46</t>
+          <t>£568.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>600x900mm Rooflight</t>
+          <t>1000x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£318.66</t>
+          <t>£734.52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£223.06</t>
+          <t>£440.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>600x1200mm Rooflight</t>
+          <t>800x800mm Rooflight</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£398.68</t>
+          <t>£359.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£239.21</t>
+          <t>£251.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>800x800mm Rooflight</t>
+          <t>600x600mm Rooflight</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£359.02</t>
+          <t>£279.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£251.31</t>
+          <t>£223.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>800x1000mm Rooflight</t>
+          <t>600x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£435.62</t>
+          <t>£483.65</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£304.93</t>
+          <t>£338.56</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>900x900mm Rooflight</t>
+          <t>800x1000mm Rooflight</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£439.54</t>
+          <t>£435.62</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£307.68</t>
+          <t>£304.93</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1000x1000mm Rooflight</t>
+          <t>1200x2000mm Rooflight</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£515.11</t>
+          <t>£1,114.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£309.07</t>
+          <t>£780.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>600x1500mm Rooflight</t>
+          <t>800x1500mm Rooflight</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£483.65</t>
+          <t>£607.67</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£338.56</t>
+          <t>£425.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>800x1200mm Rooflight Skylight</t>
+          <t>900x900mm Rooflight</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£499.36</t>
+          <t>£439.54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£349.55</t>
+          <t>£307.68</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1000x1200mm Rooflight</t>
+          <t>400x400mm Rooflight Skylight</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£603.71</t>
+          <t>£170.76</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£362.23</t>
+          <t>£136.61</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>600x1800mm Rooflight</t>
+          <t>600x900mm Rooflight</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£570.60</t>
+          <t>£318.66</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£399.42</t>
+          <t>£223.06</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>800x1500mm Rooflight</t>
+          <t>1000x1200mm Rooflight</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£607.67</t>
+          <t>£603.71</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£425.36</t>
+          <t>£362.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1000x1500mm Rooflight</t>
+          <t>500x500mm Rooflight</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£734.52</t>
+          <t>£219.36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£440.71</t>
+          <t>£175.49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -4993,29 +3414,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1000x2000mm Rooflight</t>
+          <t>1200x1800mm Rooflight</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£947.64</t>
+          <t>£1,012.51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£568.58</t>
+          <t>£708.75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5037,95 +3458,95 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1000x2500mm Rooflight</t>
+          <t>Rooflight 300x300mm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£1,170.29</t>
+          <t>£130.76</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£702.17</t>
+          <t>£84.99</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1200x1800mm Rooflight</t>
+          <t>1000x3000mm Rooflight</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£1,012.51</t>
+          <t>£1,382.03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£708.75</t>
+          <t>£829.22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1200x2000mm Rooflight</t>
+          <t>600x1800mm Rooflight</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1,114.75</t>
+          <t>£570.60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£780.33</t>
+          <t>£399.42</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1000x3000mm Rooflight</t>
+          <t>1000x2500mm Rooflight</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£1,382.03</t>
+          <t>£1,170.29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£829.22</t>
+          <t>£702.17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5147,7 +3568,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5205,7 +3626,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5227,7 +3648,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5249,7 +3670,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5271,7 +3692,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5293,7 +3714,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5315,7 +3736,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5337,7 +3758,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5359,7 +3780,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5381,7 +3802,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5403,7 +3824,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +3846,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5447,7 +3868,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5469,7 +3890,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5491,7 +3912,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5513,7 +3934,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5535,7 +3956,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
@@ -5557,7 +3978,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,9 +430,820 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£480.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£113.28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£188.94</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£382.07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£442.36</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£711.85</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£201.57</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£410.82</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£727.23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£282.29</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£357.92</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£410.93</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£391.49</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£447.74</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£526.53</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£630.21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£798.41</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£444.71</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£480.15</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£500.21</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£540.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£701.67</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£406.45</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£501.19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£538.19</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£672.95</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£872.04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£1,097.36</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£483.65</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£756.12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£870.35</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£1,366.54</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£899.15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -482,7 +1293,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -504,7 +1315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -526,7 +1337,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -548,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -570,7 +1381,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -592,7 +1403,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -614,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -636,7 +1447,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -658,7 +1469,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -680,7 +1491,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -702,7 +1513,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -724,7 +1535,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -746,7 +1557,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -768,7 +1579,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -790,7 +1601,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -812,7 +1623,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -834,7 +1645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -856,7 +1667,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -878,7 +1689,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -900,7 +1711,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -922,7 +1733,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -944,7 +1755,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -966,7 +1777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -988,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1821,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1843,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1887,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1909,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1931,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1975,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1208,7 +2019,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1230,7 +2041,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1252,7 +2063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1274,7 +2085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1296,7 +2107,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1311,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1372,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1394,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1416,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1438,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1460,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1482,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1504,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1526,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1548,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1570,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1592,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1614,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1636,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1658,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1680,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1702,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1724,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1746,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1764,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1786,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1804,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1826,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1844,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1866,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1884,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1906,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1923,12 +2734,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£969.36</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1950,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1972,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2096,249 +2907,1017 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£577.83</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>£405.22</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£714.82</t>
+          <t>£1,452.30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>£496.73</t>
+          <t>£1,152.45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£513.97</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>£370.65</t>
+          <t>£1,309.91</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£715.85</t>
+          <t>£1,011.46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>£541.02</t>
+          <t>£722.01</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£630.36</t>
+          <t>£2,039.40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£450.99</t>
+          <t>£1,631.77</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£398.61</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>£291.59</t>
-        </is>
-      </c>
+          <t>£802.04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£779.71</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>£555.62</t>
-        </is>
-      </c>
+          <t>£968.90</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£754.99</t>
+          <t>£733.36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>£457.04</t>
+          <t>£418.46</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£695.25</t>
+          <t>£968.20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>£514.73</t>
+          <t>£759.65</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£633.45</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>£493.72</t>
-        </is>
-      </c>
+          <t>£866.56</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>£1,256.60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>£998.44</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>£1,184.50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>£939.61</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>£1,134.65</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>£1,431.70</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>£1,138.60</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>£1,521.76</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>£1,751.00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>£1,396.43</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>£1,850.91</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>£1,134.87</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>£2,080.60</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>£1,662.91</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>£1,452.30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>£1,152.45</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>£1,092.38</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>£2,039.40</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>£1,631.77</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>£1,784.99</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>£867.71</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>£2,224.80</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>£1,780.58</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>£2,058.97</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>£1,415.14</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>£2,811.90</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>£2,256.44</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>£1,646.97</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>£901.33</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>£2,185.66</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>£1,168.89</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>£2,729.50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>£1,699.37</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>£3,189.91</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>£1,902.60</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>£746.75</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>£580.78</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>£807.52</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>£517.55</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>£872.41</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>£556.44</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>£1,264.84</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>£897.82</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>£1,028.97</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>£693.66</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>£1,042.36</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>£777.88</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>£609.76</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>£461.49</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>£577.83</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>£405.22</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>£714.82</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>£496.73</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>£513.97</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>£370.65</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>£715.85</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>£541.02</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>£630.36</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>£450.99</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>£398.61</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>£291.59</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>£779.71</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>£555.62</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£754.99</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>£457.04</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>£695.25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>£514.73</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>£633.45</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>£493.72</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>£577.83</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>£410.57</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2386,13 +3965,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£ 85.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>£ 115.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£ 95.00</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2404,13 +3987,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£ 130.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£ 140.00</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2422,13 +4009,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>£ 354.00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2440,13 +4031,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£ 360.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£ 350.00</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2458,13 +4053,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£ 700.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£ 500.00</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2476,13 +4075,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>£ 185.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>£ 165.00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2494,13 +4097,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>£ 395.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>£ 320.00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2512,13 +4119,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£ 580.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>£ 790.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£ 510.00</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2530,13 +4141,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£ 210.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>£ 245.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£ 220.00</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2548,13 +4163,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£ 350.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£ 310.00</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2566,13 +4185,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£ 400.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£ 410.00</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2584,13 +4207,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£ 310.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£ 350.00</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2602,13 +4229,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£ 360.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2620,13 +4251,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£ 455.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2638,13 +4273,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£ 604.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>£ 720.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2656,13 +4295,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>£ 580.00</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2674,13 +4317,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>£ 364.00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2692,13 +4339,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>£ 404.00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2710,13 +4361,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£ 410.00</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2728,13 +4383,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£ 410.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2746,13 +4405,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£ 484.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>£ 535.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£ 500.00</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2764,13 +4427,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£ 490.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>£ 590.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£ 540.00</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2782,13 +4449,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>£ 425.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>£ 360.00</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2800,13 +4471,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£ 370.00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>£ 458.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£ 390.00</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2818,13 +4493,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£ 425.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£ 455.00</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2836,13 +4515,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£ 490.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>£ 616.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£ 510.00</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2854,13 +4537,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£ 610.00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>£ 776.00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2872,13 +4559,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£ 844.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>£ 952.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£ 810.00</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2890,13 +4581,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£ 910.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2908,13 +4603,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£ 495.00</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2926,13 +4625,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£ 650.00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£ 730.00</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2944,13 +4647,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£ 620.00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£ 760.00</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2962,13 +4669,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£ 720.00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>£ 950.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2980,13 +4691,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>£ 1,520.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>£ 1,390.00</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -2998,13 +4713,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£ 1,900.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>£ 2,100.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£ 1,950.00</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3062,7 +4781,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3084,7 +4803,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3106,7 +4825,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3128,7 +4847,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3150,7 +4869,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3172,7 +4891,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3194,7 +4913,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3216,7 +4935,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3238,7 +4957,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3260,7 +4979,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3282,7 +5001,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3304,7 +5023,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3326,7 +5045,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3348,7 +5067,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3370,7 +5089,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3392,7 +5111,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3414,7 +5133,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3436,7 +5155,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3458,7 +5177,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3480,7 +5199,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3502,7 +5221,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3524,7 +5243,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3546,7 +5265,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3568,7 +5287,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3626,7 +5345,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3648,7 +5367,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3670,7 +5389,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3692,7 +5411,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3714,7 +5433,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3736,7 +5455,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3758,7 +5477,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3780,7 +5499,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3802,7 +5521,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3824,7 +5543,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3846,51 +5565,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£674.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£674.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3912,7 +5631,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3934,7 +5653,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3956,7 +5675,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
@@ -3978,7 +5697,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -469,7 +469,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,832 +1282,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£216.30</t>
+          <t>£3,037.32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£102.07</t>
+          <t>£1,851.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£172.36</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£347.24</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£403.58</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£646.58</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£183.35</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£371.27</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£661.78</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£257.36</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£327.14</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£372.78</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£357.65</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£407.32</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£477.51</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£571.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£725.04</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£362.37</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.05</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£403.39</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£435.76</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£454.31</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£490.40</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£637.25</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£369.34</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£456.80</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£491.12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£612.24</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£792.43</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£1,104.29</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£686.56</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£831.27</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£1,369.18</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£851.76</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£2,079.00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£1,164.84</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>£2,585.00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>£1,644.52</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>£3,037.32</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>£1,851.77</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2165,7 +1377,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2183,7 +1395,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2205,7 +1417,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2227,7 +1439,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2249,7 +1461,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2271,7 +1483,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2293,7 +1505,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2315,7 +1527,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2337,7 +1549,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2359,7 +1571,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2381,7 +1593,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2403,7 +1615,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2425,7 +1637,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2447,7 +1659,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2469,7 +1681,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2491,7 +1703,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2513,7 +1725,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2535,7 +1747,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +1769,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2575,7 +1787,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2597,7 +1809,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2615,7 +1827,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2637,7 +1849,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2655,7 +1867,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2677,7 +1889,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2695,7 +1907,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2717,7 +1929,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2739,7 +1951,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2761,7 +1973,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2783,7 +1995,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2017,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2039,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2057,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2079,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2097,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2119,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2141,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2163,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2185,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2207,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3017,7 +2229,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3035,7 +2247,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3053,7 +2265,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3075,7 +2287,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3097,7 +2309,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3115,7 +2327,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3137,7 +2349,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3159,7 +2371,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3177,7 +2389,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3199,7 +2411,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3217,7 +2429,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3239,7 +2451,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3261,7 +2473,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3283,7 +2495,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3305,7 +2517,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3323,7 +2535,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3345,7 +2557,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3367,7 +2579,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3389,7 +2601,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3411,7 +2623,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3433,7 +2645,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3455,7 +2667,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3477,7 +2689,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3499,7 +2711,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3521,7 +2733,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3543,7 +2755,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3565,7 +2777,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3587,7 +2799,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3609,7 +2821,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3631,7 +2843,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3653,7 +2865,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3675,7 +2887,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3697,7 +2909,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3719,7 +2931,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3741,7 +2953,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3763,7 +2975,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3785,7 +2997,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3019,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3041,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3063,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3085,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3107,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3129,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4019,7 +3231,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4041,7 +3253,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4063,7 +3275,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4085,7 +3297,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4107,7 +3319,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4129,7 +3341,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4151,7 +3363,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4173,7 +3385,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4195,7 +3407,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4217,7 +3429,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4239,7 +3451,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4261,7 +3473,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4283,7 +3495,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4305,7 +3517,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4327,7 +3539,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4349,7 +3561,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4371,7 +3583,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4393,7 +3605,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4415,7 +3627,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4437,7 +3649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4459,7 +3671,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4481,7 +3693,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4503,7 +3715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4525,7 +3737,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4547,7 +3759,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4569,7 +3781,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4591,7 +3803,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4613,7 +3825,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4635,7 +3847,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4657,7 +3869,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4679,7 +3891,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4701,7 +3913,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4723,7 +3935,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -4738,560 +3950,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regular_price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sale_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date_scraped</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>600x1200mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£398.68</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>£239.21</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>800x1200mm Rooflight Skylight</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£499.36</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£349.55</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1000x1000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£515.11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£309.07</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1000x2000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£947.64</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£568.58</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1000x1500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£734.52</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£440.71</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>800x800mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£359.02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£251.31</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>600x600mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£279.23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£223.38</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>600x1500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£483.65</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£338.56</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>800x1000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£435.62</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£304.93</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1200x2000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£1,114.75</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£780.33</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>800x1500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£607.67</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£425.36</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>900x900mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£439.54</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£307.68</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>400x400mm Rooflight Skylight</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£170.76</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£136.61</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>600x900mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£318.66</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£223.06</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1000x1200mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£603.71</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£362.23</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>500x500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£219.36</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£175.49</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1200x1200mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£705.89</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£494.12</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1200x1800mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£1,012.51</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£708.75</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1500x1500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£1,045.71</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£627.43</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Rooflight 300x300mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£130.76</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£84.99</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1000x3000mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£1,382.03</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£829.22</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>600x1800mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£570.60</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£399.42</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1000x2500mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£1,170.29</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£702.17</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1800x1800mm Rooflight</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£1,114.75</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£1,016.22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5345,7 +4006,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5367,7 +4028,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5389,7 +4050,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5411,7 +4072,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5433,7 +4094,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5455,7 +4116,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5477,7 +4138,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5499,7 +4160,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5521,7 +4182,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5543,7 +4204,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5565,7 +4226,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5587,7 +4248,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5609,7 +4270,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5631,7 +4292,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5653,7 +4314,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5675,7 +4336,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
@@ -5697,7 +4358,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -469,7 +469,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>£1,309.91</t>
+          <t>£1,271.76</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£1,631.77</t>
+          <t>£1,584.24</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4226,51 +4226,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£674.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£674.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -430,820 +430,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regular_price</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sale_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date_scraped</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£480.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£216.30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£113.28</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£188.94</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£382.07</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£442.36</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£711.85</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£201.57</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£410.82</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£727.23</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£282.29</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£357.92</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£410.93</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£391.49</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£447.74</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£526.53</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£630.21</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£798.41</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.06</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£444.71</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£480.15</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£500.21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£540.50</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£701.67</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£406.45</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£501.19</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£538.19</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£672.95</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£872.04</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£1,097.36</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£483.65</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£756.12</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£870.35</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£1,366.54</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£899.15</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1254,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,44 +471,832 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£2,585.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>£1,644.52</t>
-        </is>
-      </c>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£102.07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£172.36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£347.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£403.58</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£646.58</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£183.35</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£371.27</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£661.78</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£257.36</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£327.14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£372.78</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£357.65</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£407.32</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£477.51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£571.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£725.04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£362.37</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£403.39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£435.76</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£454.31</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£490.40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£637.25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£369.34</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£456.80</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£491.12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£612.24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£792.43</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£1,104.29</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£686.56</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£831.27</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£1,369.18</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£851.76</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£2,079.00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£1,164.84</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>£3,037.32</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>£1,851.77</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1354,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1372,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1394,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1416,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1438,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1460,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1482,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1504,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1526,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1548,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1570,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1592,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1614,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1636,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1658,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1680,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1702,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1724,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1746,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1764,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1786,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1804,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1826,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1844,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1866,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1884,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1906,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1928,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1950,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1972,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2017,7 +1994,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2016,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2034,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2056,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2074,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2096,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2118,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2140,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2162,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2184,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2206,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2224,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2242,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2264,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2286,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2304,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2326,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2348,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2366,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2388,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2406,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2428,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2450,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2472,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2494,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2512,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2534,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2556,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2578,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2600,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2622,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2644,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2666,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2688,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2710,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2732,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2754,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2776,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2798,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2820,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2842,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2864,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2886,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2908,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2930,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2952,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2974,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3019,7 +2996,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3018,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3040,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3062,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3084,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3106,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3164,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3186,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3208,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3230,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3252,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3274,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3296,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3318,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3340,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3362,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3384,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3406,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3428,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3450,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3472,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3494,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3516,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3538,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3560,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3582,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3604,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3626,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3648,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3670,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3692,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3714,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3736,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3758,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3780,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3802,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3824,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3846,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3868,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3890,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3912,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4006,7 +3983,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4005,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4027,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4049,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4071,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4093,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4115,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4137,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4159,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4181,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4203,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4225,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4247,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4269,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4291,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4313,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4335,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,15 +471,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -489,812 +493,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£216.30</t>
+          <t>£3,037.32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£102.07</t>
+          <t>£1,851.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£172.36</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£347.24</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£403.58</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£646.58</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£183.35</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£371.27</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£661.78</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£257.36</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£327.14</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£372.78</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£357.65</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£407.32</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£477.51</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£571.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£725.04</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£362.37</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.05</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£403.39</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£435.76</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£454.31</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£490.40</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£637.25</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£369.34</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£456.80</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£491.12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£612.24</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£792.43</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£1,104.29</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£686.56</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£831.27</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£1,369.18</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£851.76</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£2,079.00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£1,164.84</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>£2,585.00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>£1,644.52</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>£3,037.32</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>£1,851.77</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1311,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,17 +551,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bespoke Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£585.04</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£386.25</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1361,15 +573,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bespoke Framed Skylight for Flat Roof</t>
+          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£638.02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>£1,452.30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£1,152.45</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1379,17 +595,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300 x 300 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£229.69</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£115.65</t>
+          <t>£1,271.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1401,17 +617,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300 x 300 mm Framed Skylight for Flat Roof</t>
+          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£782.80</t>
+          <t>£1,011.46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£645.81</t>
+          <t>£722.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1423,17 +639,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>400 x 400 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£283.25</t>
+          <t>£2,039.40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£195.29</t>
+          <t>£1,584.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1445,19 +661,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>400 x 400 mm Framed Skylight for Flat Roof</t>
+          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£782.80</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£645.81</t>
-        </is>
-      </c>
+          <t>£802.04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1467,19 +679,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>400 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£546.93</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£393.42</t>
-        </is>
-      </c>
+          <t>£968.90</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1489,17 +697,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>400 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£885.80</t>
+          <t>£733.36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£693.89</t>
+          <t>£418.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1511,17 +719,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>400 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£693.19</t>
+          <t>£968.20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£457.26</t>
+          <t>£759.65</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1533,19 +741,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>400 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£1,081.50</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£849.63</t>
-        </is>
-      </c>
+          <t>£866.56</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1555,17 +759,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>400 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£1,062.96</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£732.58</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1577,17 +781,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>400 x 3000 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£1,184.50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£939.61</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1599,19 +803,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>500 x 500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£317.24</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£207.74</t>
-        </is>
-      </c>
+          <t>£1,134.65</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1621,17 +821,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>500 x 500 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£659.20</t>
+          <t>£1,431.70</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£507.01</t>
+          <t>£1,138.60</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1643,19 +843,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£616.97</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£420.65</t>
-        </is>
-      </c>
+          <t>£1,521.76</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1665,17 +861,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>500 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£1,081.50</t>
+          <t>£1,751.00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£849.63</t>
+          <t>£1,396.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1687,17 +883,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£1,165.96</t>
+          <t>£1,850.91</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£749.80</t>
+          <t>£1,134.87</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1709,17 +905,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>500 x 3000 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£1,648.00</t>
+          <t>£2,080.60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£1,309.91</t>
+          <t>£1,662.91</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1731,17 +927,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>600 x 600 mm Framed Skylight for Flat Roof</t>
+          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£782.80</t>
+          <t>£1,452.30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£609.10</t>
+          <t>£1,152.45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1753,12 +949,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>600 x 600 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£589.57</t>
+          <t>£1,092.38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1771,17 +967,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>600 x 900 mm Framed Skylight for Flat Roof</t>
+          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£782.80</t>
+          <t>£2,039.40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£610.83</t>
+          <t>£1,631.77</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1793,15 +989,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>600 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£683.01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>£1,784.99</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£867.71</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1811,17 +1011,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>600 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£606.67</t>
+          <t>£2,224.80</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£422.36</t>
+          <t>£1,780.58</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1833,15 +1033,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>600 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£770.89</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>£2,058.97</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£1,415.14</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1851,17 +1055,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>600 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£865.20</t>
+          <t>£2,811.90</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£674.86</t>
+          <t>£2,256.44</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1873,15 +1077,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>600 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£849.63</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>£1,646.97</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£901.33</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -1891,17 +1099,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>600 x 1800 mm Framed Skylight for Flat Roof</t>
+          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£1,081.50</t>
+          <t>£2,185.66</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£854.82</t>
+          <t>£1,168.89</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1913,17 +1121,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>600 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£2,729.50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£1,699.37</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1935,17 +1143,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>600 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£915.67</t>
+          <t>£3,189.91</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>£646.94</t>
+          <t>£1,902.60</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1957,17 +1165,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>600 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£1,648.00</t>
+          <t>£746.75</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>£1,309.91</t>
+          <t>£580.78</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1979,17 +1187,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>600 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£1,065.02</t>
+          <t>£807.52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>£821.47</t>
+          <t>£517.55</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2001,17 +1209,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>600 x 3000 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£1,843.70</t>
+          <t>£872.41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>£1,474.30</t>
+          <t>£556.44</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2023,15 +1231,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>750 x 750 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£670.78</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>£1,264.84</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£897.82</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -2041,17 +1253,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>800 x 800 mm Framed Skylight for Flat Roof</t>
+          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£885.80</t>
+          <t>£1,028.97</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>£693.89</t>
+          <t>£693.66</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2063,15 +1275,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>800 x 1000 mm Framed Skylight for Flat Roof</t>
+          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£849.63</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>£1,042.36</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£777.88</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -2081,17 +1297,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>800 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£1,081.50</t>
+          <t>£609.76</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>£849.63</t>
+          <t>£461.49</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2103,17 +1319,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£577.83</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£405.22</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2125,17 +1341,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
+          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£1,452.30</t>
+          <t>£714.82</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>£1,152.45</t>
+          <t>£496.73</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2147,17 +1363,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£1,648.00</t>
+          <t>£513.97</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>£1,271.76</t>
+          <t>£370.65</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2169,17 +1385,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£1,011.46</t>
+          <t>£715.85</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>£722.01</t>
+          <t>£541.02</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2191,17 +1407,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£2,039.40</t>
+          <t>£630.36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£1,584.24</t>
+          <t>£450.99</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2213,15 +1429,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£802.04</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>£398.61</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>£291.59</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -2231,15 +1451,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£968.90</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>£779.71</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>£555.62</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -2249,17 +1473,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£733.36</t>
+          <t>£754.99</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>£418.46</t>
+          <t>£457.04</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2271,17 +1495,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
+          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£968.20</t>
+          <t>£695.25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>£759.65</t>
+          <t>£514.73</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2293,15 +1517,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£866.56</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>£633.45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>£493.72</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>2026-04-21</t>
@@ -2311,800 +1539,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£577.83</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£410.57</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>£1,184.50</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>£939.61</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>£1,134.65</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>£1,431.70</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>£1,138.60</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>£1,521.76</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>£1,751.00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>£1,396.43</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>£1,850.91</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>£1,134.87</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>£2,080.60</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>£1,662.91</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>£1,452.30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>£1,152.45</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>£1,092.38</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>£2,039.40</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>£1,631.77</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>£1,784.99</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>£867.71</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>£2,224.80</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>£1,780.58</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>£2,058.97</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>£1,415.14</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>£2,811.90</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>£2,256.44</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>£1,646.97</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>£901.33</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>£2,185.66</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>£1,168.89</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>£2,729.50</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>£1,699.37</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>£3,189.91</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>£1,902.60</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>£746.75</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>£580.78</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>£807.52</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>£517.55</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>£872.41</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>£556.44</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>£1,264.84</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>£897.82</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>£1,028.97</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>£693.66</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>£1,042.36</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>£777.88</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>£609.76</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>£461.49</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>£577.83</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>£405.22</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>£714.82</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>£496.73</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>£513.97</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>£370.65</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>£715.85</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>£541.02</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>£630.36</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>£450.99</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>£398.61</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>£291.59</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>£779.71</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>£555.62</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>£754.99</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>£457.04</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>£695.25</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>£514.73</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>£633.45</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>£493.72</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>£577.83</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>£410.57</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,1010 +551,1774 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>Bespoke Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£585.04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£386.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
+          <t>Bespoke Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£1,452.30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£1,152.45</t>
-        </is>
-      </c>
+          <t>£638.02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>300 x 300 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£1,648.00</t>
+          <t>£229.69</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£1,271.76</t>
+          <t>£115.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>300 x 300 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£1,011.46</t>
+          <t>£782.80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£722.01</t>
+          <t>£645.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 400 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£2,039.40</t>
+          <t>£283.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£1,584.24</t>
+          <t>£195.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>400 x 400 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£802.04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>£782.80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£645.81</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>400 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£968.90</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>£546.93</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£393.42</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>400 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£733.36</t>
+          <t>£885.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£418.46</t>
+          <t>£693.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£968.20</t>
+          <t>£693.19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£759.65</t>
+          <t>£457.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>400 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£866.56</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>£1,081.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£849.63</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£1,062.96</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£732.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 3000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1,184.50</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£939.61</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>500 x 500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1,134.65</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>£317.24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£207.74</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>500 x 500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£1,431.70</t>
+          <t>£659.20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£1,138.60</t>
+          <t>£507.01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£1,521.76</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>£616.97</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£420.65</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>500 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£1,751.00</t>
+          <t>£1,081.50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£1,396.43</t>
+          <t>£849.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£1,850.91</t>
+          <t>£1,165.96</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£1,134.87</t>
+          <t>£749.80</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
+          <t>500 x 3000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£2,080.60</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£1,662.91</t>
+          <t>£1,309.91</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 600 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£1,452.30</t>
+          <t>£782.80</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£1,152.45</t>
+          <t>£609.10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>600 x 600 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£1,092.38</t>
+          <t>£589.57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 900 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£2,039.40</t>
+          <t>£782.80</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£1,631.77</t>
+          <t>£610.83</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1,784.99</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£867.71</t>
-        </is>
-      </c>
+          <t>£683.01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£2,224.80</t>
+          <t>£606.67</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£1,780.58</t>
+          <t>£422.36</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£2,058.97</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£1,415.14</t>
-        </is>
-      </c>
+          <t>£770.89</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 1200 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£2,811.90</t>
+          <t>£865.20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£2,256.44</t>
+          <t>£674.86</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£1,646.97</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£901.33</t>
-        </is>
-      </c>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 1800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£2,185.66</t>
+          <t>£1,081.50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£1,168.89</t>
+          <t>£854.82</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£2,729.50</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,699.37</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£3,189.91</t>
+          <t>£915.67</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>£1,902.60</t>
+          <t>£646.94</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
+          <t>600 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£746.75</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>£580.78</t>
+          <t>£1,309.91</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£807.52</t>
+          <t>£1,065.02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>£517.55</t>
+          <t>£821.47</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 3000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£872.41</t>
+          <t>£1,843.70</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>£556.44</t>
+          <t>£1,474.30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>750 x 750 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£1,264.84</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£897.82</t>
-        </is>
-      </c>
+          <t>£670.78</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£1,028.97</t>
+          <t>£885.80</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>£693.66</t>
+          <t>£693.89</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£1,042.36</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£777.88</t>
-        </is>
-      </c>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1200 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£609.76</t>
+          <t>£1,081.50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>£461.49</t>
+          <t>£849.63</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£577.83</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>£405.22</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£714.82</t>
+          <t>£1,452.30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>£496.73</t>
+          <t>£1,152.45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£513.97</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>£370.65</t>
+          <t>£1,309.91</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£715.85</t>
+          <t>£1,011.46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>£541.02</t>
+          <t>£722.01</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£630.36</t>
+          <t>£2,039.40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£450.99</t>
+          <t>£1,631.77</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£398.61</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>£291.59</t>
-        </is>
-      </c>
+          <t>£802.04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£779.71</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>£555.62</t>
-        </is>
-      </c>
+          <t>£968.90</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£754.99</t>
+          <t>£733.36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>£457.04</t>
+          <t>£418.46</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£695.25</t>
+          <t>£968.20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>£514.73</t>
+          <t>£759.65</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£633.45</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>£493.72</t>
-        </is>
-      </c>
+          <t>£866.56</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>£1,256.60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>£998.44</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>£1,184.50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>£939.61</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>£1,134.65</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>£1,431.70</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>£1,138.60</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>£1,521.76</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>£1,751.00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>£1,396.43</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>£1,850.91</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>£1,134.87</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>£2,080.60</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>£1,662.91</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>£1,452.30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>£1,118.88</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>£1,092.38</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>£2,039.40</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>£1,631.77</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>£1,784.99</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>£867.71</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>£2,224.80</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>£1,780.58</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>£2,058.97</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>£1,415.14</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>£2,811.90</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>£2,256.44</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>£1,646.97</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>£901.33</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>£2,185.66</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>£1,168.89</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>£2,729.50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>£1,699.37</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>£3,189.91</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>£1,902.60</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>£746.75</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>£580.78</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>£807.52</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>£517.55</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>£872.41</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>£556.44</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>£1,264.84</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>£897.82</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>£1,028.97</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>£693.66</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>£1,042.36</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>£777.88</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>£609.76</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>£461.49</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>£577.83</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>£405.22</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>£714.82</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>£496.73</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>£513.97</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>£370.65</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>£715.85</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>£541.02</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>£630.36</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>£450.99</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>£398.61</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>£291.59</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>£779.71</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>£555.62</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£754.99</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>£457.04</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>£695.25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>£514.73</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>£633.45</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>£493.72</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>£577.83</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>£410.57</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1612,7 +2376,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1634,7 +2398,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1656,7 +2420,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1678,7 +2442,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1700,7 +2464,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1722,7 +2486,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1744,7 +2508,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1766,7 +2530,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1788,7 +2552,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1810,7 +2574,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1832,7 +2596,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1854,7 +2618,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1876,7 +2640,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1898,7 +2662,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1920,7 +2684,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1937,12 +2701,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£ 580.00</t>
+          <t>£ 800.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1964,7 +2728,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2750,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2772,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2794,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2816,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2838,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2882,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2904,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2926,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2948,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2970,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2992,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2250,7 +3014,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2272,7 +3036,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2294,7 +3058,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2316,7 +3080,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2338,7 +3102,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2360,7 +3124,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2431,7 +3195,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2453,7 +3217,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2475,7 +3239,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2497,7 +3261,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2519,7 +3283,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2541,7 +3305,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2563,7 +3327,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2585,7 +3349,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2607,7 +3371,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2629,7 +3393,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2651,7 +3415,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2673,7 +3437,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2695,7 +3459,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2717,7 +3481,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2739,7 +3503,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2761,7 +3525,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -2783,7 +3547,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,19 +471,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£2,585.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>£1,644.52</t>
-        </is>
-      </c>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>2026-04-27</t>
@@ -493,20 +489,812 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£102.07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£172.36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£347.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£403.58</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£646.58</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£183.35</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£371.27</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£661.78</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£257.36</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£327.14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£372.78</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£357.65</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£407.32</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£477.51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£571.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£725.04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£362.37</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£403.39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£435.76</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£454.31</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£490.40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£637.25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£369.34</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£456.80</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£491.12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£612.24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£792.43</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£1,104.29</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£686.56</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£831.27</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£1,369.18</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£851.76</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£2,079.00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£1,164.84</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>£3,037.32</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>£1,851.77</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,832 +471,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£375.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£216.30</t>
+          <t>£3,037.32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£102.07</t>
+          <t>£1,851.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£260.70</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£172.36</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£515.60</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£347.24</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£657.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£403.58</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£1,000.55</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£646.58</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£293.70</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£183.35</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£587.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£371.27</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£1,105.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£661.78</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£378.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£257.36</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£489.50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£327.14</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£576.40</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£372.78</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£545.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£357.65</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£407.32</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£477.51</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£867.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£571.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£1,002.10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£725.04</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£546.70</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£362.37</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£592.90</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£398.05</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£710.60</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£403.39</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>£600.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£435.76</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>£658.90</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£454.31</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>£731.50</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£490.40</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>£954.80</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£637.25</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>£693.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£369.34</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£456.80</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>£823.90</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£491.12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>£979.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£612.24</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>£1,208.90</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£792.43</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>£1,758.90</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£1,104.29</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>£676.50</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£438.42</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£686.56</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>£1,688.50</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£831.27</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>£1,969.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£1,369.18</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>£1,569.70</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£851.76</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>£2,079.00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£1,164.84</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>£2,585.00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>£1,644.52</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>£3,037.32</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>£1,851.77</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1354,7 +566,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1372,7 +584,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1394,7 +606,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1416,7 +628,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1438,7 +650,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1460,7 +672,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1482,7 +694,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +716,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1526,7 +738,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1548,7 +760,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1570,7 +782,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1592,7 +804,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1614,7 +826,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1636,7 +848,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1658,7 +870,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1680,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1702,7 +914,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1724,7 +936,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1746,7 +958,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1764,7 +976,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1786,7 +998,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1016,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1038,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1056,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1078,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1096,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1118,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1140,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1162,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1184,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1206,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2016,7 +1228,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2034,7 +1246,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2056,7 +1268,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2074,7 +1286,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2096,7 +1308,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2118,7 +1330,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2140,7 +1352,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2162,7 +1374,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2184,7 +1396,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2206,7 +1418,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2224,7 +1436,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2242,7 +1454,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2264,7 +1476,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2286,7 +1498,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2304,7 +1516,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2326,7 +1538,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2348,7 +1560,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2366,7 +1578,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2388,7 +1600,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2406,7 +1618,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2428,7 +1640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2450,7 +1662,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2472,7 +1684,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2494,7 +1706,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2512,7 +1724,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2534,7 +1746,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2556,7 +1768,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2578,7 +1790,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2600,7 +1812,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2622,7 +1834,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2644,7 +1856,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2666,7 +1878,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2688,7 +1900,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2710,7 +1922,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2732,7 +1944,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2754,7 +1966,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2776,7 +1988,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2010,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2032,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2054,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2076,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2098,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2120,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2142,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2164,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2186,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2208,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3018,7 +2230,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3040,7 +2252,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3062,7 +2274,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3084,7 +2296,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3106,7 +2318,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3164,7 +2376,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3186,7 +2398,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3208,7 +2420,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3230,7 +2442,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3252,7 +2464,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3274,7 +2486,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3296,7 +2508,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3318,7 +2530,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3340,7 +2552,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3362,7 +2574,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3384,7 +2596,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3406,7 +2618,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3428,7 +2640,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3450,7 +2662,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3472,7 +2684,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3494,7 +2706,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3516,7 +2728,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3538,7 +2750,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3560,7 +2772,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3582,7 +2794,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3604,7 +2816,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3626,7 +2838,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3648,7 +2860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3670,7 +2882,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3692,7 +2904,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3714,7 +2926,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3736,7 +2948,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3758,7 +2970,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3780,7 +2992,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3014,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3036,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3058,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3080,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3102,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3124,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3195,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +3217,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4027,7 +3239,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4049,7 +3261,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4071,7 +3283,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4093,7 +3305,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4115,7 +3327,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4137,7 +3349,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4159,7 +3371,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4181,7 +3393,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4203,7 +3415,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4225,7 +3437,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4247,7 +3459,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4269,7 +3481,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4291,7 +3503,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4313,7 +3525,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4335,7 +3547,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -7,7 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skylights Rooflight" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lanterns Direct" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skylight Depot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skylight Factory" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hi-Sky" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hi-Tech" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skylights Rooflight" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,26 +430,4898 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Triple Glazed Flat and Pitched Roof Skylight Online Calculator</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Custom Size Frameless Modular Skylights (Flat / Pitched Roof)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£480.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300 x 300 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£113.28</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>400 x 400 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£188.94</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£382.07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>400 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£442.36</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>400 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£711.85</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>500 x 500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£201.57</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£410.82</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>500 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£727.23</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>600 x 600 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£282.29</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>600 x 900 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£357.92</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>600 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£410.93</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£391.49</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£447.74</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£526.53</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>600 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£630.21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>600 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£798.41</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>800 x 800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£444.71</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£480.15</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£500.21</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£540.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>800 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£701.67</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1000 x 1000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£406.45</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£501.19</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£538.19</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£672.95</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£872.04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£1,097.36</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£483.65</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£756.12</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£870.35</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£1,366.54</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm LD Frameless Triple Glazed Flat Roof Skylight</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£899.15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£102.07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£172.36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£347.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£403.58</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£646.58</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£183.35</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£371.27</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£661.78</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£257.36</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£327.14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£372.78</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£357.65</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£407.32</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£477.51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£571.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£725.04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£362.37</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£403.39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£435.76</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£454.31</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£490.40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£637.25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£369.34</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£456.80</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£491.12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£612.24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£792.43</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£1,104.29</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£686.56</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£831.27</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£1,369.18</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£851.76</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£2,079.00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£1,164.84</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>£3,037.32</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>£1,851.77</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bespoke Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£585.04</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£386.25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bespoke Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£638.02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300 x 300 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£229.69</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£115.65</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300 x 300 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£782.80</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£645.81</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>400 x 400 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£283.25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£195.29</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>400 x 400 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£782.80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£645.81</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>400 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£546.93</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£393.42</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>400 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£885.80</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£693.89</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>400 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£693.19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£457.26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>400 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£1,081.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>400 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£1,062.96</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£732.58</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>400 x 3000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£1,256.60</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£998.44</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>500 x 500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£317.24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£207.74</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>500 x 500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£659.20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£507.01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£616.97</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£420.65</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>500 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£1,081.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£1,165.96</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£749.80</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>500 x 3000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£1,648.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£1,309.91</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>600 x 600 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£782.80</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£609.10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>600 x 600 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£589.57</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>600 x 900 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£782.80</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£610.83</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>600 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£683.01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>600 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£606.67</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£422.36</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>600 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£770.89</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>600 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£865.20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£674.86</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£1,081.50</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£854.82</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£1,256.60</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£998.44</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>600 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£915.67</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£646.94</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>600 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,648.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£1,309.91</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>600 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£1,065.02</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£821.47</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>600 x 3000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£1,843.70</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£1,474.30</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>750 x 750 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£670.78</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>800 x 800 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£885.80</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£693.89</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£1,081.50</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£1,256.60</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>£998.44</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>£1,452.30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>£1,152.45</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>£1,648.00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>£1,309.91</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>£1,011.46</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>£722.01</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>£2,039.40</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>£1,631.77</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>£802.04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>£968.90</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>£733.36</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>£418.46</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>£968.20</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>£759.65</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>£866.56</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>£1,256.60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>£998.44</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>£1,184.50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>£939.61</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>£1,134.65</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>£1,431.70</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>£1,138.60</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>£1,521.76</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>£1,751.00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>£1,396.43</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>£1,850.91</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>£1,134.87</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>£2,080.60</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>£1,662.91</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>£1,452.30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>£1,152.45</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>£1,092.38</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>£2,039.40</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>£1,631.77</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>£1,784.99</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>£867.71</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>£2,224.80</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>£1,780.58</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>£2,058.97</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>£1,415.14</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>£2,811.90</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>£2,256.44</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>£1,646.97</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>£901.33</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>£2,185.66</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>£1,168.89</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>£2,729.50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>£1,699.37</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>£3,189.91</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>£1,902.60</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>£746.75</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>£580.78</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>£807.52</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>£517.55</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>£872.41</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>£556.44</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>£1,264.84</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>£897.82</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>£1,028.97</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>£693.66</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>£1,042.36</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>£777.88</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>£609.76</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>£461.49</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>£577.83</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>£405.22</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>£714.82</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>£496.73</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>£513.97</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>£370.65</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>£715.85</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>£541.02</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>£630.36</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>£450.99</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>£398.61</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>£291.59</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>£779.71</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>£555.62</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£754.99</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>£457.04</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>£695.25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>£514.73</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>£633.45</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>£493.72</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>£577.83</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>£410.57</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£ 115.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£ 95.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£ 140.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£ 354.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£ 350.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£ 500.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£ 185.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£ 395.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£ 320.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£ 790.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£ 510.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£ 245.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£ 220.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£ 310.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£ 410.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£ 350.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£ 720.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£ 800.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£ 364.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£ 404.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£ 410.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£ 535.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£ 500.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£ 590.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£ 540.00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 900 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£ 425.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£ 360.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£ 458.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£ 390.00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£ 455.00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£ 616.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£ 510.00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£ 776.00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£ 660.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£ 952.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£ 810.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£ 495.00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£ 730.00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£ 760.00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£ 950.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£ 1,520.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£ 1,390.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Flat Roof Triple Glazed Skylight 1500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£ 2,100.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£ 1,950.00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>600x900mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£318.66</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£223.06</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>600x1800mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£570.60</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£399.42</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1000x2500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£1170.29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£702.17</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1800x1800mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£1114.75</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£1016.22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1000x1200mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£603.71</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£362.23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1500x1500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£1045.71</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£627.43</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1000x3000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£1382.03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£829.22</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>800x800mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£359.02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£251.31</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>600x600mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£279.23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£223.38</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>500x500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£219.36</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£175.49</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>400x400mm Rooflight Skylight</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£170.76</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£136.61</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rooflight 300x300mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£130.76</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£84.99</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1000x1500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£734.52</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£440.71</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1000x2000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£947.64</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£568.58</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1000x1000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£515.11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£309.07</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>800x1200mm Rooflight Skylight</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£499.36</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£349.55</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1200x1200mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£705.89</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£494.12</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>800x1000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£435.62</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£304.93</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>600x1500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£483.65</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£338.56</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>600x1200mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£398.68</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£239.21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1200x2000mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£1114.75</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£780.33</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1200x1800mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£1012.51</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£708.75</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>800x1500mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£607.67</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£425.36</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>900x900mm Rooflight</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£439.54</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£307.68</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>regular_price</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sale_price</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>date_scraped</t>
         </is>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -469,7 +469,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CLEARANCE SALE - 1500 x 2500 mm Frameless Skylight for Flat Roof - Solar Grey - Custom 1 Unit</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>£2,729.50</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>£2,480.00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3997,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4019,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4014,12 +4036,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£ 354.00</t>
+          <t>£ 320.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4063,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4085,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4107,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4146,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£ 510.00</t>
+          <t>£ 650.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4173,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4195,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4212,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£ 410.00</t>
+          <t>£ 390.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4239,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4283,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4305,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4327,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4322,12 +4344,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£ 364.00</t>
+          <t>£ 334.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4366,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£ 404.00</t>
+          <t>£ 384.00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4393,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4415,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4437,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4459,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4481,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4503,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4525,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4547,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4569,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4591,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4608,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>£ 1,250.00</t>
+          <t>£ 1,150.00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4635,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4657,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4679,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4701,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4723,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4745,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4803,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4825,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4847,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4869,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4891,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4913,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4935,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4957,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4979,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -4979,7 +5001,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5023,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5045,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5089,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5111,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5133,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5155,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5177,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5199,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5221,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5243,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5265,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5287,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5309,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5367,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5389,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5411,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5433,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5455,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5477,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5499,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5521,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5543,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5565,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5587,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5609,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5631,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5653,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5675,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5697,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5719,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -469,7 +469,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4696,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
+          <t>£ 900.00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hi-Sky" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hi-Tech" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skylights Rooflight" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy Glass and Steel" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -491,7 +492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -513,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -535,7 +536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -557,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -579,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -601,7 +602,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -623,7 +624,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -645,7 +646,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -667,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -689,7 +690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -711,7 +712,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -733,7 +734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -755,7 +756,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -777,7 +778,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -799,7 +800,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -821,7 +822,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -843,7 +844,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -865,7 +866,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -887,7 +888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -909,7 +910,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -931,7 +932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -953,7 +954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -975,7 +976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -997,7 +998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1020,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1086,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1152,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1174,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1196,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1240,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1294,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1316,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1338,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1360,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1382,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1404,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1426,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1448,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1470,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1492,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1514,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1536,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1558,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1580,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1602,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1624,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1646,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1668,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1690,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1712,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1734,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1756,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1778,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1800,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1822,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1844,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1866,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1888,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1910,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1932,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1954,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1976,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2020,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2042,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2064,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2086,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2108,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2166,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2184,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2206,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2228,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2250,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2294,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2316,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2360,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2382,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2426,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2448,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2470,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2514,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2536,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2558,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2576,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2598,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2616,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2638,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2656,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2678,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2696,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2718,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2740,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2762,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2784,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2806,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2828,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2846,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2868,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2886,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2908,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2930,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2952,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2974,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2996,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3018,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3036,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3054,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3076,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3098,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3116,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3160,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3178,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3200,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3218,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3240,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3262,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3284,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3306,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3324,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3346,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3368,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3390,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3412,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3434,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3456,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3478,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3500,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3544,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3588,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3610,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3632,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3654,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3676,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3698,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3720,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3742,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3764,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3786,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3808,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3830,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3852,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3874,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3896,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3918,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3940,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3998,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4020,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4042,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4086,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4108,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4130,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4152,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4174,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4196,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4218,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4240,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4262,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4284,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4306,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4328,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4350,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4372,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4394,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4416,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4438,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4460,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4482,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4504,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4526,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4548,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4570,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4592,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4614,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4636,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4658,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4680,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4702,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4724,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4746,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4804,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4826,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4848,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4870,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4892,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4914,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4936,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4958,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4980,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5002,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5024,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5046,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5068,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5090,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5112,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5134,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5156,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5178,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5200,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5222,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5244,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5266,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5310,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5368,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5390,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5412,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5434,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5456,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5478,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5500,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5522,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5544,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5566,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5588,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5609,7 +5610,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5632,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5654,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5676,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5698,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5720,791 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 300 X 300 mm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£136.13</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>£108.90</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 400 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£257.13</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£205.70</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£548.63</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£438.90</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£697.13</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£557.70</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£1,091.86</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£779.90</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 500 X 500 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£239.25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£191.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 500 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£622.22</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£460.90</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 500 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£1,043.63</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£834.90</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 600 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£384.62</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£284.90</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 900 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£507.38</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£405.90</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£548.63</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£438.90</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£576.13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£460.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 1800 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£663.52</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£510.40</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£713.63</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£570.90</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 2500 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£864.88</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£691.90</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£1,230.46</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£878.90</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1000 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£462.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 800 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£548.63</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£438.90</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£644.88</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£515.90</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£686.13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£548.90</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1800 m</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£713.63</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£570.90</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£782.38</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£625.90</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 900 X 900 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£563.75</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£451.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 1000 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£569.25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£455.40</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£658.63</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£526.90</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£768.63</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£614.90</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£961.13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 2500 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£1,236.13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1,841.13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£1,472.90</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1200 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£686.13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£548.90</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1200 X 1800 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£1,043.63</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£834.90</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1500 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£1,372.80</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£1,097.80</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1500 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£2,047.38</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£1,637.90</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1500 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£3,011.25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£2,200.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -470,7 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£375.00</t>
+          <t>£340.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -3988,17 +3988,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£ 115.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>£ 95.00</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4006,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>£ 140.00</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4032,17 +4024,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>£ 320.00</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4054,17 +4042,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>£ 350.00</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4076,17 +4060,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>£ 500.00</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4078,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£ 185.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>£ 165.00</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4120,17 +4096,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£ 395.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>£ 320.00</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4142,17 +4114,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£ 790.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>£ 650.00</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4164,17 +4132,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£ 245.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>£ 220.00</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4150,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>£ 310.00</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4208,17 +4168,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>£ 390.00</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4230,17 +4186,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
           <t>£ 350.00</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4252,17 +4204,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>£ 420.00</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4222,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>£ 450.00</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4296,17 +4240,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£ 720.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>£ 660.00</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4258,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>£ 800.00</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4340,17 +4276,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>£ 334.00</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4362,17 +4294,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
           <t>£ 384.00</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4384,17 +4312,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>£ 410.00</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4406,17 +4330,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>£ 460.00</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4348,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£ 535.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>£ 500.00</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4450,17 +4366,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£ 590.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>£ 540.00</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4472,17 +4384,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£ 425.00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>£ 360.00</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4494,17 +4402,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£ 458.00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>£ 390.00</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4516,17 +4420,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
           <t>£ 455.00</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4538,17 +4438,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£ 616.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£ 510.00</t>
-        </is>
-      </c>
+          <t>£ 590.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4560,17 +4456,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£ 776.00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>£ 660.00</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4582,17 +4474,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£ 952.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
           <t>£ 810.00</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4604,17 +4492,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£ 1,250.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
           <t>£ 1,150.00</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4510,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
           <t>£ 495.00</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4648,17 +4528,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
           <t>£ 730.00</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4670,17 +4546,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
           <t>£ 760.00</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4692,17 +4564,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£ 950.00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>£ 900.00</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4714,17 +4582,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£ 1,520.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>£ 1,390.00</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4736,17 +4600,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£ 2,100.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
           <t>£ 1,950.00</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4664,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4686,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4708,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4730,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4752,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4774,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4796,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4818,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4840,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5002,7 +4862,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5024,7 +4884,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5046,7 +4906,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5068,7 +4928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5090,7 +4950,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5112,7 +4972,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5134,7 +4994,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5016,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5038,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5060,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5104,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5126,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5148,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5170,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5228,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5412,14 +5272,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1800mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1200mm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5429,19 +5289,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£376.80</t>
+          <t>£337.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1800mm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5451,12 +5311,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£337.00</t>
+          <t>£376.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5338,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5360,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5382,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5404,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5426,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5448,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5470,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5492,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5514,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5536,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5558,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5580,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5768,17 +5628,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£136.13</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>£108.90</t>
-        </is>
-      </c>
+          <t>£113.44</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5790,17 +5646,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£257.13</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£205.70</t>
-        </is>
-      </c>
+          <t>£214.28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5812,17 +5664,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£548.63</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>£438.90</t>
-        </is>
-      </c>
+          <t>£457.19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5834,17 +5682,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£697.13</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>£557.70</t>
-        </is>
-      </c>
+          <t>£580.94</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5856,17 +5700,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£1,091.86</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£779.90</t>
-        </is>
-      </c>
+          <t>£909.88</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5878,17 +5718,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£239.25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£191.40</t>
-        </is>
-      </c>
+          <t>£199.38</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5900,17 +5736,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£622.22</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>£460.90</t>
-        </is>
-      </c>
+          <t>£518.52</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5922,17 +5754,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£1,043.63</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>£834.90</t>
-        </is>
-      </c>
+          <t>£869.69</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5944,17 +5772,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£384.62</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>£284.90</t>
-        </is>
-      </c>
+          <t>£320.52</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5966,17 +5790,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£507.38</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>£405.90</t>
-        </is>
-      </c>
+          <t>£422.82</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -5988,17 +5808,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£548.63</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£438.90</t>
-        </is>
-      </c>
+          <t>£457.19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6010,17 +5826,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£576.13</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>£460.90</t>
-        </is>
-      </c>
+          <t>£480.11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6032,17 +5844,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£663.52</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>£510.40</t>
-        </is>
-      </c>
+          <t>£552.93</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6054,17 +5862,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£713.63</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>£570.90</t>
-        </is>
-      </c>
+          <t>£594.69</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6076,17 +5880,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£864.88</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>£691.90</t>
-        </is>
-      </c>
+          <t>£720.73</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6098,17 +5898,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£1,230.46</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>£878.90</t>
-        </is>
-      </c>
+          <t>£1,025.38</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6120,17 +5916,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£577.50</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>£462.00</t>
-        </is>
-      </c>
+          <t>£481.25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6142,17 +5934,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£548.63</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>£438.90</t>
-        </is>
-      </c>
+          <t>£457.19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6164,17 +5952,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£644.88</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>£515.90</t>
-        </is>
-      </c>
+          <t>£537.40</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6186,17 +5970,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£686.13</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£548.90</t>
-        </is>
-      </c>
+          <t>£571.78</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6208,17 +5988,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£713.63</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£570.90</t>
-        </is>
-      </c>
+          <t>£594.69</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6230,17 +6006,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£782.38</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£625.90</t>
-        </is>
-      </c>
+          <t>£651.98</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6252,17 +6024,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£563.75</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>£451.00</t>
-        </is>
-      </c>
+          <t>£469.79</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6274,17 +6042,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£569.25</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£455.40</t>
-        </is>
-      </c>
+          <t>£474.38</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6296,17 +6060,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£658.63</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>£526.90</t>
-        </is>
-      </c>
+          <t>£548.86</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6318,17 +6078,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£768.63</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£614.90</t>
-        </is>
-      </c>
+          <t>£640.53</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6340,17 +6096,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£961.13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>£768.90</t>
-        </is>
-      </c>
+          <t>£800.94</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6362,17 +6114,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£1,236.13</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>£988.90</t>
-        </is>
-      </c>
+          <t>£1,030.11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6384,17 +6132,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£1,841.13</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>£1,472.90</t>
-        </is>
-      </c>
+          <t>£1,534.28</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6406,17 +6150,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£686.13</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£548.90</t>
-        </is>
-      </c>
+          <t>£571.78</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6428,17 +6168,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£1,043.63</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£834.90</t>
-        </is>
-      </c>
+          <t>£869.69</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6450,17 +6186,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£1,372.80</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>£1,097.80</t>
-        </is>
-      </c>
+          <t>£1,144.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6472,17 +6204,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£2,047.38</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£1,637.90</t>
-        </is>
-      </c>
+          <t>£1,706.15</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -6494,17 +6222,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£3,011.25</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£2,200.00</t>
-        </is>
-      </c>
+          <t>£2,509.38</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -470,7 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -487,12 +487,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£340.00</t>
+          <t>£375.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£386.25</t>
+          <t>£375.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -3988,13 +3988,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>£ 115.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>£ 95.00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4006,13 +4010,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>£ 165.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>£ 140.00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4024,13 +4032,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>£ 320.00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4042,13 +4054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>£ 350.00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4060,13 +4076,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>£ 500.00</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4078,13 +4098,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>£ 185.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>£ 165.00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4096,13 +4120,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>£ 395.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>£ 320.00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4114,13 +4142,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>£ 790.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>£ 650.00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4132,13 +4164,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>£ 245.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>£ 220.00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4150,13 +4186,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>£ 380.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>£ 310.00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4168,13 +4208,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>£ 390.00</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4186,13 +4230,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>£ 450.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>£ 350.00</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4204,13 +4252,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>£ 420.00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4222,13 +4274,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>£ 450.00</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4240,13 +4296,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>£ 720.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>£ 660.00</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4258,13 +4318,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>£ 800.00</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4276,13 +4340,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>£ 420.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>£ 334.00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4294,13 +4362,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>£ 454.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>£ 384.00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4312,13 +4384,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>£ 460.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>£ 410.00</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4330,13 +4406,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>£ 460.00</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4348,13 +4428,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>£ 535.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>£ 500.00</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4366,13 +4450,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>£ 590.00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>£ 540.00</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4384,13 +4472,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>£ 425.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>£ 360.00</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4402,13 +4494,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>£ 458.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>£ 390.00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4420,13 +4516,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>£ 480.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>£ 455.00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4438,13 +4538,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>£ 616.00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>£ 590.00</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4456,13 +4560,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>£ 776.00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>£ 660.00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4474,13 +4582,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>£ 952.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>£ 810.00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4492,13 +4604,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>£ 1,250.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>£ 1,150.00</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4510,13 +4626,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>£ 520.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>£ 495.00</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4528,13 +4648,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>£ 850.00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>£ 730.00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4546,13 +4670,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>£ 820.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>£ 760.00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4564,13 +4692,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>£ 950.00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>£ 900.00</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4582,13 +4714,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>£ 1,520.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>£ 1,390.00</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4600,13 +4736,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>£ 2,100.00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>£ 1,950.00</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4804,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4826,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4848,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4870,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4892,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4914,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4936,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4958,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4980,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4862,7 +5002,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4884,7 +5024,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4906,7 +5046,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5068,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4950,7 +5090,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4972,7 +5112,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -4994,7 +5134,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5156,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5178,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5200,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5222,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5244,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5266,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5310,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5368,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5390,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5412,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5434,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5316,51 +5456,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 600mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1200mm x 1200mm</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£520.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£303.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1200mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 600mm x 1200mm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£520.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£303.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5522,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5544,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5566,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5448,51 +5588,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£674.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£674.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5654,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5676,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5698,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5720,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5774,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5792,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5810,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5828,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5846,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5864,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5882,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5900,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5918,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5936,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5954,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5972,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5990,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5868,7 +6008,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5886,7 +6026,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5904,7 +6044,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5922,7 +6062,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5940,7 +6080,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5958,7 +6098,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5976,7 +6116,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -5994,7 +6134,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6152,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6170,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6188,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6206,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6224,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6242,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6260,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6278,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6296,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6314,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6332,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6350,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6368,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -470,7 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£375.00</t>
+          <t>£386.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£ 95.00</t>
+          <t>£ 95.00Inc VAT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£ 140.00</t>
+          <t>£ 140.00Inc VAT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£ 320.00</t>
+          <t>£ 320.00Inc VAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£ 350.00</t>
+          <t>£ 350.00Inc VAT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4081,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£ 500.00</t>
+          <t>£ 500.00Inc VAT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£ 165.00</t>
+          <t>£ 165.00Inc VAT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£ 320.00</t>
+          <t>£ 320.00Inc VAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£ 650.00</t>
+          <t>£ 650.00Inc VAT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£ 220.00</t>
+          <t>£ 220.00Inc VAT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£ 310.00</t>
+          <t>£ 310.00Inc VAT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4213,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£ 390.00</t>
+          <t>£ 390.00Inc VAT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£ 350.00</t>
+          <t>£ 350.00Inc VAT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
+          <t>£ 420.00Inc VAT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
+          <t>£ 450.00Inc VAT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£ 660.00</t>
+          <t>£ 660.00Inc VAT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£ 800.00</t>
+          <t>£ 800.00Inc VAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£ 334.00</t>
+          <t>£ 334.00Inc VAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£ 384.00</t>
+          <t>£ 384.00Inc VAT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4389,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£ 410.00</t>
+          <t>£ 410.00Inc VAT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4411,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
+          <t>£ 460.00Inc VAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4433,12 +4433,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£ 500.00</t>
+          <t>£ 500.00Inc VAT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£ 540.00</t>
+          <t>£ 540.00Inc VAT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£ 360.00</t>
+          <t>£ 360.00Inc VAT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4499,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>£ 390.00</t>
+          <t>£ 390.00Inc VAT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£ 455.00</t>
+          <t>£ 455.00Inc VAT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£ 590.00</t>
+          <t>£ 590.00Inc VAT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£ 660.00</t>
+          <t>£ 660.00Inc VAT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£ 810.00</t>
+          <t>£ 810.00Inc VAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4609,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>£ 1,150.00</t>
+          <t>£ 1,150.00Inc VAT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4631,12 +4631,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>£ 495.00</t>
+          <t>£ 495.00Inc VAT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4653,12 +4653,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>£ 730.00</t>
+          <t>£ 730.00Inc VAT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4675,12 +4675,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>£ 760.00</t>
+          <t>£ 760.00Inc VAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>£ 900.00</t>
+          <t>£ 900.00Inc VAT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>£ 1,390.00</t>
+          <t>£ 1,390.00Inc VAT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>£ 1,950.00</t>
+          <t>£ 1,950.00Inc VAT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1800mm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£337.00</t>
+          <t>£376.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1800mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1200mm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£376.80</t>
+          <t>£337.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5588,51 +5588,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£674.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£674.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5654,51 +5654,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1000mm</t>
+          <t>Flat Rooflights &amp; Skylights 1500mm x 1500mm</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£800.00</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£314.00</t>
+          <t>£691.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1500mm x 1500mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1000mm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£1,250.00</t>
+          <t>£800.00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£691.00</t>
+          <t>£314.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -470,7 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3988,17 +3988,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£ 115.00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>£ 95.00Inc VAT</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4006,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£ 165.00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>£ 140.00Inc VAT</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4032,17 +4024,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>£ 320.00Inc VAT</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4054,17 +4042,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>£ 350.00Inc VAT</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4076,17 +4060,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>£ 500.00Inc VAT</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4078,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£ 185.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>£ 165.00Inc VAT</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4120,17 +4096,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£ 395.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>£ 320.00Inc VAT</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4142,17 +4114,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£ 790.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>£ 650.00Inc VAT</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4164,17 +4132,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£ 245.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>£ 220.00Inc VAT</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4150,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£ 380.00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>£ 310.00Inc VAT</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4208,17 +4168,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>£ 390.00Inc VAT</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4230,17 +4186,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£ 450.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
           <t>£ 350.00Inc VAT</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4252,17 +4204,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>£ 420.00Inc VAT</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4222,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>£ 450.00Inc VAT</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4296,17 +4240,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£ 720.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>£ 660.00Inc VAT</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4258,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>£ 800.00Inc VAT</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4340,17 +4276,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£ 420.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>£ 334.00Inc VAT</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4362,17 +4294,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£ 454.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
           <t>£ 384.00Inc VAT</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4384,17 +4312,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£ 460.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>£ 410.00Inc VAT</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4406,17 +4330,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>£ 460.00Inc VAT</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4348,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£ 535.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>£ 500.00Inc VAT</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4450,17 +4366,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£ 590.00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>£ 540.00Inc VAT</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4472,17 +4384,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£ 425.00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>£ 360.00Inc VAT</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4494,17 +4402,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£ 458.00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>£ 390.00Inc VAT</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4516,17 +4420,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£ 480.00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
           <t>£ 455.00Inc VAT</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4538,17 +4438,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£ 616.00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
           <t>£ 590.00Inc VAT</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4560,17 +4456,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£ 776.00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>£ 660.00Inc VAT</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4582,17 +4474,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£ 952.00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
           <t>£ 810.00Inc VAT</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4604,17 +4492,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£ 1,250.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
           <t>£ 1,150.00Inc VAT</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4510,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£ 520.00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
           <t>£ 495.00Inc VAT</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4648,17 +4528,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£ 850.00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
           <t>£ 730.00Inc VAT</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4670,17 +4546,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£ 820.00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
           <t>£ 760.00Inc VAT</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4692,17 +4564,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£ 950.00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>£ 900.00Inc VAT</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4714,17 +4582,13 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£ 1,520.00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
           <t>£ 1,390.00Inc VAT</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4736,17 +4600,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£ 2,100.00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
           <t>£ 1,950.00Inc VAT</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4664,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4686,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4708,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4730,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4752,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4774,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4796,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4818,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4840,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5002,7 +4862,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5024,7 +4884,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5046,7 +4906,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5068,7 +4928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5090,7 +4950,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5112,7 +4972,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5134,7 +4994,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5016,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5038,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5060,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5104,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5126,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5148,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5170,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5228,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5272,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5294,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5316,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5338,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5360,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5382,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5404,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5426,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5448,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5470,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5492,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5654,51 +5514,51 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1500mm x 1500mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1000mm</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£1,250.00</t>
+          <t>£800.00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£691.00</t>
+          <t>£314.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1000mm</t>
+          <t>Flat Rooflights &amp; Skylights 1500mm x 1500mm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£800.00</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£314.00</t>
+          <t>£691.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5580,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5634,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5652,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5670,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5688,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5706,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5724,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5742,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5760,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5778,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5796,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5814,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5832,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5850,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6008,7 +5868,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6026,7 +5886,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6044,7 +5904,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6062,7 +5922,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6080,7 +5940,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6098,7 +5958,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6116,7 +5976,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6134,7 +5994,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6012,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6030,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6048,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6066,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6084,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6102,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6120,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6138,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6156,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6174,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6192,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6210,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6228,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -470,7 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4444,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5272,14 +5272,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1800mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1200mm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5289,19 +5289,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£376.80</t>
+          <t>£337.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 800mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 800mm x 1800mm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£337.00</t>
+          <t>£376.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5448,51 +5448,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£650.00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£674.00</t>
+          <t>£381.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flat Rooflights &amp; Skylights 1000mm x 1200mm</t>
+          <t>Flat Rooflights &amp; Skylights 1000mm x 2500mm</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£650.00</t>
+          <t>£1,200.00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£381.00</t>
+          <t>£674.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>

--- a/Weekly_Prices.xlsx
+++ b/Weekly_Prices.xlsx
@@ -470,7 +470,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -1255,9 +1255,864 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Custom Triple Glazed Frameless Skylight (Flat Roof)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£375.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 300 x 300 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£216.30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>£102.07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 400 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£260.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>£172.36</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£515.60</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>£347.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£657.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£403.58</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 400 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£1,000.55</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£646.58</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£293.70</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£183.35</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£587.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>£371.27</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£1,105.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>£661.78</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 600 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£378.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£257.36</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 900 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£489.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£327.14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£576.40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>£372.78</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£545.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£357.65</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£577.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£407.32</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£477.51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£867.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>£571.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 600 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£1,002.10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>£725.04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 800 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£546.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£362.37</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£592.90</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£398.05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£710.60</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£403.39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£600.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£435.76</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£658.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£454.31</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£731.50</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£490.40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 800 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£954.80</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£637.25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1000 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£693.00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£369.34</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£768.90</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£456.80</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£823.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£491.12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£979.00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£612.24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1,208.90</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>£792.43</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1000 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£1,758.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£1,104.29</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1200 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£676.50</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£438.42</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 1800 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£988.90</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>£686.56</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£1,688.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£831.27</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1200 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£1,969.00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£1,369.18</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 1500 mm</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>£1,569.70</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£851.76</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2000 mm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>£2,079.00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£1,164.84</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 2500 mm</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>£2,585.00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>£1,644.52</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Triple Glazed Frameless Skylight (Flat Roof) 1500 x 3000 mm</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>£3,037.32</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>£1,851.77</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1268,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,1032 +2151,1796 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>Bespoke Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£585.04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£386.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
+          <t>Bespoke Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>£1,452.30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>£1,152.45</t>
-        </is>
-      </c>
+          <t>£638.02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>300 x 300 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>£1,648.00</t>
+          <t>£229.69</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£1,309.91</t>
+          <t>£115.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>300 x 300 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>£1,011.46</t>
+          <t>£782.80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£722.01</t>
+          <t>£645.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 400 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£2,039.40</t>
+          <t>£283.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£1,631.77</t>
+          <t>£195.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>400 x 400 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>£1,162.96</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>£782.80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£645.81</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>400 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>£1,404.91</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>£546.93</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>£393.42</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>400 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>£733.36</t>
+          <t>£885.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£418.46</t>
+          <t>£693.89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£968.20</t>
+          <t>£693.19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£759.65</t>
+          <t>£457.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>400 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>£1,256.51</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>£1,081.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>£849.63</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>£1,256.60</t>
+          <t>£1,062.96</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£998.44</t>
+          <t>£732.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
+          <t>400 x 3000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>£1,184.50</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£939.61</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>500 x 500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>£1,645.24</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>£317.24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>£207.74</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>500 x 500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>£1,431.70</t>
+          <t>£659.20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£1,138.60</t>
+          <t>£507.01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£2,206.55</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>£616.97</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>£420.65</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>500 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>£1,751.00</t>
+          <t>£1,081.50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£1,396.43</t>
+          <t>£849.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>£1,850.91</t>
+          <t>£1,165.96</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£1,134.87</t>
+          <t>£749.80</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
+          <t>500 x 3000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>£2,080.60</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£1,662.91</t>
+          <t>£1,309.91</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 600 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>£1,452.30</t>
+          <t>£782.80</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£1,152.45</t>
+          <t>£609.10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+          <t>600 x 600 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>£1,583.95</t>
+          <t>£854.88</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 900 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£2,039.40</t>
+          <t>£782.80</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£1,631.77</t>
+          <t>£610.83</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1,784.99</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>£867.71</t>
-        </is>
-      </c>
+          <t>£990.36</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>£2,224.80</t>
+          <t>£606.67</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£1,780.58</t>
+          <t>£422.36</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>£2,058.97</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>£1,415.14</t>
-        </is>
-      </c>
+          <t>£1,117.79</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
+          <t>600 x 1200 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£2,811.90</t>
+          <t>£865.20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£2,256.44</t>
+          <t>£674.86</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>£1,646.97</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>£901.33</t>
-        </is>
-      </c>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 1800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>£2,185.66</t>
+          <t>£1,081.50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£1,168.89</t>
+          <t>£854.82</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£2,729.50</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,699.37</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>£3,189.91</t>
+          <t>£915.67</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>£1,902.60</t>
+          <t>£646.94</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
+          <t>600 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>£746.75</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>£580.78</t>
+          <t>£1,309.91</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£807.52</t>
+          <t>£1,065.02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>£517.55</t>
+          <t>£821.47</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>600 x 3000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>£872.41</t>
+          <t>£1,843.70</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>£556.44</t>
+          <t>£1,474.30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>750 x 750 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>£1,264.84</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£897.82</t>
-        </is>
-      </c>
+          <t>£972.63</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>£1,028.97</t>
+          <t>£885.80</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>£693.66</t>
+          <t>£693.89</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£1,042.36</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£777.88</t>
-        </is>
-      </c>
+          <t>£849.63</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1200 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>£609.76</t>
+          <t>£1,081.50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>£461.49</t>
+          <t>£849.63</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>£577.83</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>£405.22</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 1800 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>£714.82</t>
+          <t>£1,452.30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>£496.73</t>
+          <t>£1,152.45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>£513.97</t>
+          <t>£1,648.00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>£370.65</t>
+          <t>£1,309.91</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>£715.85</t>
+          <t>£1,011.46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>£541.02</t>
+          <t>£722.01</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>800 x 2500 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£630.36</t>
+          <t>£2,039.40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£450.99</t>
+          <t>£1,631.77</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>900 x 900 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>£398.61</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>£291.59</t>
-        </is>
-      </c>
+          <t>£1,162.96</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>900 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>£779.71</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>£555.62</t>
-        </is>
-      </c>
+          <t>£1,404.91</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>£754.99</t>
+          <t>£733.36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>£457.04</t>
+          <t>£418.46</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>£695.25</t>
+          <t>£968.20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>£514.73</t>
+          <t>£759.65</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1000 mm Brett Martin Fixed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>£633.45</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>£493.72</t>
-        </is>
-      </c>
+          <t>£1,256.51</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+          <t>1000 x 1200 mm Framed Skylight for Flat Roof</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£577.83</t>
+          <t>£1,256.60</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>£410.57</t>
+          <t>£998.44</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>1000 x 1500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>£1,184.50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>£939.61</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>£1,645.24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>£1,431.70</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>£1,138.60</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>£2,206.55</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>£1,751.00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>£1,396.43</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>£1,850.91</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>£1,134.87</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1000 x 3000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>£2,080.60</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>£1,662.91</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>£1,452.30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>£1,152.45</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Brett Martin Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>£1,583.95</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>£2,039.40</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>£1,631.77</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>£1,784.99</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>£867.71</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1200 x 2000 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>£2,224.80</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>£1,780.58</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>£2,058.97</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>£1,415.14</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1200 x 2500 mm Framed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>£2,811.90</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>£2,256.44</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1500 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>£1,646.97</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>£901.33</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1500 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>£2,185.66</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>£1,168.89</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1500 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>£2,729.50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>£1,699.37</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1500 x 3000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>£3,189.91</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>£1,902.60</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Brett Martin Bespoke Fixed Skylight for Flat Roof</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>£746.75</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>£580.78</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1000 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>£807.52</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>£517.55</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1000 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>£872.41</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>£556.44</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1000 x 2500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>£1,264.84</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>£897.82</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1000 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>£1,028.97</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>£693.66</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1200 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>£1,042.36</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>£777.88</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>600 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>£609.76</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>£461.49</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>600 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>£577.83</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>£405.22</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1200 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>£714.82</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>£496.73</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>600 x 900 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>£513.97</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>£370.65</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>600 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>£715.85</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>£541.02</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>800 x 1000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>£630.36</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>£450.99</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>600 x 600 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>£398.61</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>£291.59</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>800 x 2000 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>£779.71</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>£555.62</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>800 x 1200 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>£754.99</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>£457.04</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>800 x 1800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>£695.25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>£514.73</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>800 x 1500 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>£633.45</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>£493.72</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>800 x 800 mm Frameless Skylight for Flat Roof - Triple Glazed</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>£577.83</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>£410.57</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>CLEARANCE SALE - 1500 x 2500 mm Frameless Skylight for Flat Roof - Solar Grey - Custom 1 Unit</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>£2,729.50</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>£2,480.00</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2392,7 +4011,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2414,7 +4033,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2436,7 +4055,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2458,7 +4077,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2480,7 +4099,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2502,7 +4121,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2524,7 +4143,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2546,7 +4165,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2568,7 +4187,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2590,7 +4209,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2612,7 +4231,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2634,7 +4253,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2656,7 +4275,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2678,7 +4297,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +4319,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2722,7 +4341,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2744,7 +4363,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2766,7 +4385,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2788,7 +4407,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2810,7 +4429,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2832,7 +4451,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2854,7 +4473,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2876,7 +4495,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2898,7 +4517,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2956,7 +4575,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -2978,7 +4597,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3000,7 +4619,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3022,7 +4641,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3044,7 +4663,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3066,7 +4685,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3088,7 +4707,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3110,7 +4729,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3132,7 +4751,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3154,7 +4773,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +4795,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3198,7 +4817,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3220,7 +4839,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3242,7 +4861,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3264,7 +4883,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3286,7 +4905,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3308,7 +4927,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -3323,9 +4942,644 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regular_price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>date_scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 300 X 300 mm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>£113.44</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 400 mm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>£214.28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>£457.19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>£580.94</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 400 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>£909.88</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 500 X 500 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>£199.38</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 500 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>£518.52</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 500 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>£869.69</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 600 mm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>£320.52</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 900 mm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>£422.82</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>£457.19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>£480.11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 1800 mm</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>£552.93</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>£594.69</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 2500 mm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>£720.73</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 600 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>£1,025.38</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1000 mm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>£481.25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 800 mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>£457.19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>£537.40</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>£571.78</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 1800 m</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>£594.69</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 800 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>£651.98</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 900 X 900 mm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>£469.79</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 1000 mm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>£474.38</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>£548.86</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>£640.53</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>£800.94</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 2500 mm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>£1,030.11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1000 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>£1,534.28</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1200 X 1200 mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>£571.78</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1200 X 1800 mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>£869.69</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1500 X 1500 mm</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>£1,144.00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1500 X 2000 mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>£1,706.15</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triple Glazed Skylight 1500 X 3000 mm</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>£2,509.38</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>